--- a/TJ_Surgery_2018_2023_Pitchers_FILLED.xlsx
+++ b/TJ_Surgery_2018_2023_Pitchers_FILLED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6772c73964c7b6d/TJPROJECT599/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_213335CB1137CA1B1EF52B8EAEA92375D8FA6F64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480A32FF-0703-4951-8F13-5F4EC6C97B40}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_213335CB1137CA1B1EF52B8EAEA92375D8FA6F64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41BDC118-5871-4149-9427-87CD73D12982}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="MLB Pitchers 2018-2023 TJ" sheetId="1" r:id="rId1"/>
     <sheet name="Unmatched - Check Manually" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="244">
   <si>
     <t>Player</t>
   </si>
@@ -744,6 +757,15 @@
   </si>
   <si>
     <t>No seasons found for [2015, 2016, 2017]</t>
+  </si>
+  <si>
+    <t>K-BB% Diff.(+ improvement)</t>
+  </si>
+  <si>
+    <t>FIP Diff. (- improvement)</t>
+  </si>
+  <si>
+    <t>ERA Diff. (- improvement)</t>
   </si>
 </sst>
 </file>
@@ -799,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -815,6 +837,8 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V159"/>
+  <dimension ref="A1:Y159"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1138,9 +1162,12 @@
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="23" max="23" width="13.6328125" customWidth="1"/>
+    <col min="24" max="24" width="13.26953125" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,8 +1234,17 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1275,8 +1311,20 @@
       <c r="V2">
         <v>22487</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W2" s="11">
+        <f>S2-R2</f>
+        <v>-0.25179999999999936</v>
+      </c>
+      <c r="X2" s="11">
+        <f>U2-T2</f>
+        <v>0.68320000000000025</v>
+      </c>
+      <c r="Y2" s="12">
+        <f>Q2-P2</f>
+        <v>3.2299999999999995E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -1343,8 +1391,20 @@
       <c r="V3">
         <v>20666</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W3" s="11">
+        <f>S3-R3</f>
+        <v>1.0273000000000003</v>
+      </c>
+      <c r="X3" s="11">
+        <f>U3-T3</f>
+        <v>0.72279999999999989</v>
+      </c>
+      <c r="Y3" s="12">
+        <f>Q3-P3</f>
+        <v>-6.610000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -1411,8 +1471,20 @@
       <c r="V4">
         <v>18684</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W4" s="11">
+        <f t="shared" ref="W4:W67" si="0">S4-R4</f>
+        <v>1.7988999999999997</v>
+      </c>
+      <c r="X4" s="11">
+        <f t="shared" ref="X4:X67" si="1">U4-T4</f>
+        <v>0.93080000000000007</v>
+      </c>
+      <c r="Y4" s="12">
+        <f t="shared" ref="Y4:Y67" si="2">Q4-P4</f>
+        <v>-6.5999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1479,8 +1551,20 @@
       <c r="V5">
         <v>17759</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W5" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.837299999999999</v>
+      </c>
+      <c r="X5" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.88590000000000035</v>
+      </c>
+      <c r="Y5" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.9499999999999993E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -1547,8 +1631,20 @@
       <c r="V6">
         <v>19755</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W6" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.72840000000000016</v>
+      </c>
+      <c r="X6" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.59620000000000006</v>
+      </c>
+      <c r="Y6" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.2000000000000075E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1615,8 +1711,20 @@
       <c r="V7">
         <v>26260</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W7" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3563000000000001</v>
+      </c>
+      <c r="X7" s="11">
+        <f t="shared" si="1"/>
+        <v>1.2186999999999997</v>
+      </c>
+      <c r="Y7" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.17349999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -1683,8 +1791,20 @@
       <c r="V8">
         <v>19388</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W8" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3820000000000001</v>
+      </c>
+      <c r="X8" s="11">
+        <f t="shared" si="1"/>
+        <v>2.7460999999999998</v>
+      </c>
+      <c r="Y8" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.0799999999999975E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
@@ -1751,8 +1871,20 @@
       <c r="V9">
         <v>21483</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W9" s="11">
+        <f t="shared" si="0"/>
+        <v>0.43530000000000024</v>
+      </c>
+      <c r="X9" s="11">
+        <f t="shared" si="1"/>
+        <v>0.36799999999999988</v>
+      </c>
+      <c r="Y9" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.6900000000000005E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
@@ -1819,8 +1951,20 @@
       <c r="V10">
         <v>3548</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W10" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0724</v>
+      </c>
+      <c r="X10" s="11">
+        <f t="shared" si="1"/>
+        <v>2.7701000000000002</v>
+      </c>
+      <c r="Y10" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.26719999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
@@ -1873,8 +2017,20 @@
       <c r="V11">
         <v>21541</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W11" s="11">
+        <f t="shared" si="0"/>
+        <v>-4.6406000000000001</v>
+      </c>
+      <c r="X11" s="11">
+        <f t="shared" si="1"/>
+        <v>-4.7678000000000003</v>
+      </c>
+      <c r="Y11" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.1899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -1941,8 +2097,20 @@
       <c r="V12">
         <v>15488</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W12" s="11">
+        <f t="shared" si="0"/>
+        <v>1.3751999999999995</v>
+      </c>
+      <c r="X12" s="11">
+        <f t="shared" si="1"/>
+        <v>1.0051000000000001</v>
+      </c>
+      <c r="Y12" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.1600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -2009,8 +2177,20 @@
       <c r="V13">
         <v>15463</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W13" s="11">
+        <f t="shared" si="0"/>
+        <v>-6.676000000000001</v>
+      </c>
+      <c r="X13" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.2272999999999996</v>
+      </c>
+      <c r="Y13" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1900000000000022E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
@@ -2077,8 +2257,20 @@
       <c r="V14">
         <v>19716</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W14" s="11">
+        <f t="shared" si="0"/>
+        <v>1.6860999999999997</v>
+      </c>
+      <c r="X14" s="11">
+        <f t="shared" si="1"/>
+        <v>-5.0400000000000666E-2</v>
+      </c>
+      <c r="Y14" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.8600000000000014E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
@@ -2145,8 +2337,20 @@
       <c r="V15">
         <v>19754</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W15" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.5919000000000003</v>
+      </c>
+      <c r="X15" s="11">
+        <f t="shared" si="1"/>
+        <v>-2.4100000000000676E-2</v>
+      </c>
+      <c r="Y15" s="12">
+        <f t="shared" si="2"/>
+        <v>9.900000000000006E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>59</v>
       </c>
@@ -2213,8 +2417,20 @@
       <c r="V16">
         <v>25174</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W16" s="11">
+        <f t="shared" si="0"/>
+        <v>4.8302000000000005</v>
+      </c>
+      <c r="X16" s="11">
+        <f t="shared" si="1"/>
+        <v>2.48</v>
+      </c>
+      <c r="Y16" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.6199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
@@ -2281,8 +2497,20 @@
       <c r="V17">
         <v>15440</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W17" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.3780999999999994</v>
+      </c>
+      <c r="X17" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.87199999999999989</v>
+      </c>
+      <c r="Y17" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2300000000000005E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>63</v>
       </c>
@@ -2349,8 +2577,20 @@
       <c r="V18">
         <v>10954</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W18" s="11">
+        <f t="shared" si="0"/>
+        <v>1.4655</v>
+      </c>
+      <c r="X18" s="11">
+        <f t="shared" si="1"/>
+        <v>1.5456999999999999</v>
+      </c>
+      <c r="Y18" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.15029999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
@@ -2403,8 +2643,20 @@
       <c r="V19">
         <v>18376</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W19" s="11">
+        <f t="shared" si="0"/>
+        <v>-3.3517000000000001</v>
+      </c>
+      <c r="X19" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.7330000000000001</v>
+      </c>
+      <c r="Y19" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.9500000000000006E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>66</v>
       </c>
@@ -2471,8 +2723,20 @@
       <c r="V20">
         <v>16358</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W20" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.54640000000000022</v>
+      </c>
+      <c r="X20" s="11">
+        <f t="shared" si="1"/>
+        <v>-7.1299999999999919E-2</v>
+      </c>
+      <c r="Y20" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.1300000000000012E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>67</v>
       </c>
@@ -2512,8 +2776,20 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W21" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>69</v>
       </c>
@@ -2580,8 +2856,20 @@
       <c r="V22">
         <v>19200</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W22" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.3230000000000004</v>
+      </c>
+      <c r="X22" s="11">
+        <f t="shared" si="1"/>
+        <v>0.54539999999999988</v>
+      </c>
+      <c r="Y22" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.10700000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>70</v>
       </c>
@@ -2648,8 +2936,20 @@
       <c r="V23">
         <v>24937</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W23" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.14090000000000025</v>
+      </c>
+      <c r="X23" s="11">
+        <f t="shared" si="1"/>
+        <v>0.57830000000000004</v>
+      </c>
+      <c r="Y23" s="12">
+        <f t="shared" si="2"/>
+        <v>6.6999999999999976E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>71</v>
       </c>
@@ -2716,8 +3016,20 @@
       <c r="V24">
         <v>15038</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W24" s="11">
+        <f t="shared" si="0"/>
+        <v>1.7767999999999997</v>
+      </c>
+      <c r="X24" s="11">
+        <f t="shared" si="1"/>
+        <v>1.7515000000000001</v>
+      </c>
+      <c r="Y24" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.6000000000000012E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>72</v>
       </c>
@@ -2784,8 +3096,20 @@
       <c r="V25">
         <v>15043</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W25" s="11">
+        <f t="shared" si="0"/>
+        <v>1.4355000000000002</v>
+      </c>
+      <c r="X25" s="11">
+        <f t="shared" si="1"/>
+        <v>1.2277</v>
+      </c>
+      <c r="Y25" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.2699999999999992E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>74</v>
       </c>
@@ -2852,8 +3176,20 @@
       <c r="V26">
         <v>11486</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W26" s="11">
+        <f t="shared" si="0"/>
+        <v>3.71999999999999E-2</v>
+      </c>
+      <c r="X26" s="11">
+        <f t="shared" si="1"/>
+        <v>0.11670000000000069</v>
+      </c>
+      <c r="Y26" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.09E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>75</v>
       </c>
@@ -2920,8 +3256,20 @@
       <c r="V27">
         <v>22176</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W27" s="11">
+        <f t="shared" si="0"/>
+        <v>6.2308000000000003</v>
+      </c>
+      <c r="X27" s="11">
+        <f t="shared" si="1"/>
+        <v>2.1320999999999994</v>
+      </c>
+      <c r="Y27" s="12">
+        <f t="shared" si="2"/>
+        <v>3.39E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3336,20 @@
       <c r="V28">
         <v>17677</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W28" s="11">
+        <f t="shared" si="0"/>
+        <v>1.7359999999999998</v>
+      </c>
+      <c r="X28" s="11">
+        <f t="shared" si="1"/>
+        <v>1.7364000000000002</v>
+      </c>
+      <c r="Y28" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.11019999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>77</v>
       </c>
@@ -3056,8 +3416,20 @@
       <c r="V29">
         <v>21455</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W29" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.9924000000000004</v>
+      </c>
+      <c r="X29" s="11">
+        <f t="shared" si="1"/>
+        <v>-2.0006999999999997</v>
+      </c>
+      <c r="Y29" s="12">
+        <f t="shared" si="2"/>
+        <v>7.6800000000000007E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>79</v>
       </c>
@@ -3124,8 +3496,20 @@
       <c r="V30">
         <v>17578</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W30" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.3489999999999998</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.57760000000000034</v>
+      </c>
+      <c r="Y30" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.2099999999999987E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>80</v>
       </c>
@@ -3192,8 +3576,20 @@
       <c r="V31">
         <v>27473</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W31" s="11">
+        <f t="shared" si="0"/>
+        <v>-11.2408</v>
+      </c>
+      <c r="X31" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.26469999999999994</v>
+      </c>
+      <c r="Y31" s="12">
+        <f t="shared" si="2"/>
+        <v>1.7499999999999988E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>82</v>
       </c>
@@ -3260,8 +3656,20 @@
       <c r="V32">
         <v>21290</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W32" s="11">
+        <f t="shared" si="0"/>
+        <v>27.7179</v>
+      </c>
+      <c r="X32" s="11">
+        <f t="shared" si="1"/>
+        <v>13.2315</v>
+      </c>
+      <c r="Y32" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>83</v>
       </c>
@@ -3328,8 +3736,20 @@
       <c r="V33">
         <v>18384</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W33" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0324999999999998</v>
+      </c>
+      <c r="X33" s="11">
+        <f t="shared" si="1"/>
+        <v>1.6171000000000002</v>
+      </c>
+      <c r="Y33" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.24690000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>84</v>
       </c>
@@ -3396,8 +3816,20 @@
       <c r="V34">
         <v>10058</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W34" s="11">
+        <f t="shared" si="0"/>
+        <v>5.0729999999999995</v>
+      </c>
+      <c r="X34" s="11">
+        <f t="shared" si="1"/>
+        <v>2.1342999999999996</v>
+      </c>
+      <c r="Y34" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.1199999999999994E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
@@ -3464,8 +3896,20 @@
       <c r="V35">
         <v>22264</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W35" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2612999999999999</v>
+      </c>
+      <c r="X35" s="11">
+        <f t="shared" si="1"/>
+        <v>0.20310000000000006</v>
+      </c>
+      <c r="Y35" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.15659999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
@@ -3532,8 +3976,20 @@
       <c r="V36">
         <v>5097</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W36" s="11">
+        <f t="shared" si="0"/>
+        <v>9.0346000000000011</v>
+      </c>
+      <c r="X36" s="11">
+        <f t="shared" si="1"/>
+        <v>6.64</v>
+      </c>
+      <c r="Y36" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.15530000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>89</v>
       </c>
@@ -3600,8 +4056,20 @@
       <c r="V37">
         <v>19345</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W37" s="11">
+        <f t="shared" si="0"/>
+        <v>3.994699999999999</v>
+      </c>
+      <c r="X37" s="11">
+        <f t="shared" si="1"/>
+        <v>0.45709999999999962</v>
+      </c>
+      <c r="Y37" s="12">
+        <f t="shared" si="2"/>
+        <v>6.7299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>91</v>
       </c>
@@ -3668,8 +4136,20 @@
       <c r="V38">
         <v>19742</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W38" s="11">
+        <f t="shared" si="0"/>
+        <v>0.35760000000000014</v>
+      </c>
+      <c r="X38" s="11">
+        <f t="shared" si="1"/>
+        <v>6.9799999999999862E-2</v>
+      </c>
+      <c r="Y38" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.3E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>92</v>
       </c>
@@ -3736,8 +4216,20 @@
       <c r="V39">
         <v>19374</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W39" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2061999999999999</v>
+      </c>
+      <c r="X39" s="11">
+        <f t="shared" si="1"/>
+        <v>2.4161000000000001</v>
+      </c>
+      <c r="Y39" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.14350000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>93</v>
       </c>
@@ -3804,8 +4296,20 @@
       <c r="V40">
         <v>18769</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W40" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.3223999999999996</v>
+      </c>
+      <c r="X40" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.5297999999999998</v>
+      </c>
+      <c r="Y40" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.8700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>94</v>
       </c>
@@ -3860,8 +4364,20 @@
       <c r="V41">
         <v>27474</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W41" s="11">
+        <f t="shared" si="0"/>
+        <v>5.1780999999999997</v>
+      </c>
+      <c r="X41" s="11">
+        <f t="shared" si="1"/>
+        <v>5.1345999999999998</v>
+      </c>
+      <c r="Y41" s="12">
+        <f t="shared" si="2"/>
+        <v>0.14069999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>95</v>
       </c>
@@ -3928,8 +4444,20 @@
       <c r="V42">
         <v>21183</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W42" s="11">
+        <f t="shared" si="0"/>
+        <v>-4.6400000000000219E-2</v>
+      </c>
+      <c r="X42" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.5244</v>
+      </c>
+      <c r="Y42" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.2500000000000006E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>97</v>
       </c>
@@ -3996,8 +4524,20 @@
       <c r="V43">
         <v>17610</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W43" s="11">
+        <f t="shared" si="0"/>
+        <v>0.93770000000000042</v>
+      </c>
+      <c r="X43" s="11">
+        <f t="shared" si="1"/>
+        <v>0.52419999999999956</v>
+      </c>
+      <c r="Y43" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.11720000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>98</v>
       </c>
@@ -4050,8 +4590,20 @@
       <c r="V44">
         <v>16390</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W44" s="11">
+        <f t="shared" si="0"/>
+        <v>-4.1013000000000002</v>
+      </c>
+      <c r="X44" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.9575</v>
+      </c>
+      <c r="Y44" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.2455</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
@@ -4118,8 +4670,20 @@
       <c r="V45">
         <v>19278</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W45" s="11">
+        <f t="shared" si="0"/>
+        <v>2.0132000000000003</v>
+      </c>
+      <c r="X45" s="11">
+        <f t="shared" si="1"/>
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="Y45" s="12">
+        <f t="shared" si="2"/>
+        <v>3.2899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>101</v>
       </c>
@@ -4186,8 +4750,20 @@
       <c r="V46">
         <v>12828</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W46" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27559999999999985</v>
+      </c>
+      <c r="X46" s="11">
+        <f t="shared" si="1"/>
+        <v>0.31279999999999974</v>
+      </c>
+      <c r="Y46" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.0200000000000015E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>102</v>
       </c>
@@ -4254,8 +4830,20 @@
       <c r="V47" s="2">
         <v>14444</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W47" s="11">
+        <f t="shared" si="0"/>
+        <v>0.25999999999999979</v>
+      </c>
+      <c r="X47" s="11">
+        <f t="shared" si="1"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="Y47" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.9999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>105</v>
       </c>
@@ -4322,8 +4910,20 @@
       <c r="V48">
         <v>4301</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W48" s="11">
+        <f t="shared" si="0"/>
+        <v>0.6648000000000005</v>
+      </c>
+      <c r="X48" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.3963000000000001</v>
+      </c>
+      <c r="Y48" s="12">
+        <f t="shared" si="2"/>
+        <v>5.0599999999999978E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>106</v>
       </c>
@@ -4390,8 +4990,20 @@
       <c r="V49">
         <v>22175</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W49" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.6359000000000004</v>
+      </c>
+      <c r="X49" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.6899999999999995</v>
+      </c>
+      <c r="Y49" s="12">
+        <f t="shared" si="2"/>
+        <v>6.3699999999999993E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>107</v>
       </c>
@@ -4458,8 +5070,20 @@
       <c r="V50">
         <v>15552</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W50" s="11">
+        <f t="shared" si="0"/>
+        <v>0.79289999999999994</v>
+      </c>
+      <c r="X50" s="11">
+        <f t="shared" si="1"/>
+        <v>1.5124</v>
+      </c>
+      <c r="Y50" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.11460000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>108</v>
       </c>
@@ -4526,8 +5150,20 @@
       <c r="V51">
         <v>20099</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W51" s="11">
+        <f t="shared" si="0"/>
+        <v>1.0203000000000007</v>
+      </c>
+      <c r="X51" s="11">
+        <f t="shared" si="1"/>
+        <v>0.60079999999999956</v>
+      </c>
+      <c r="Y51" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>109</v>
       </c>
@@ -4594,8 +5230,20 @@
       <c r="V52">
         <v>17034</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W52" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.1235000000000004</v>
+      </c>
+      <c r="X52" s="11">
+        <f t="shared" si="1"/>
+        <v>-2.4174000000000002</v>
+      </c>
+      <c r="Y52" s="12">
+        <f t="shared" si="2"/>
+        <v>8.1199999999999994E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>111</v>
       </c>
@@ -4662,8 +5310,20 @@
       <c r="V53">
         <v>16269</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W53" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.0876999999999999</v>
+      </c>
+      <c r="X53" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.30940000000000012</v>
+      </c>
+      <c r="Y53" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.2099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>112</v>
       </c>
@@ -4730,8 +5390,20 @@
       <c r="V54">
         <v>11752</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W54" s="11">
+        <f t="shared" si="0"/>
+        <v>0.59790000000000054</v>
+      </c>
+      <c r="X54" s="11">
+        <f t="shared" si="1"/>
+        <v>0.51499999999999968</v>
+      </c>
+      <c r="Y54" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.1899999999999983E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>113</v>
       </c>
@@ -4784,8 +5456,20 @@
       <c r="V55">
         <v>8410</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W55" s="11">
+        <f t="shared" si="0"/>
+        <v>-5.0090000000000003</v>
+      </c>
+      <c r="X55" s="11">
+        <f t="shared" si="1"/>
+        <v>-4.5278999999999998</v>
+      </c>
+      <c r="Y55" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.15429999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>114</v>
       </c>
@@ -4852,8 +5536,20 @@
       <c r="V56">
         <v>20045</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W56" s="11">
+        <f t="shared" si="0"/>
+        <v>-6.9971999999999994</v>
+      </c>
+      <c r="X56" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.3615999999999997</v>
+      </c>
+      <c r="Y56" s="12">
+        <f t="shared" si="2"/>
+        <v>6.3600000000000004E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>115</v>
       </c>
@@ -4920,8 +5616,20 @@
       <c r="V57">
         <v>27463</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W57" s="11">
+        <f t="shared" si="0"/>
+        <v>0.48060000000000036</v>
+      </c>
+      <c r="X57" s="11">
+        <f t="shared" si="1"/>
+        <v>0.28459999999999974</v>
+      </c>
+      <c r="Y57" s="12">
+        <f t="shared" si="2"/>
+        <v>7.8199999999999992E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -4988,8 +5696,20 @@
       <c r="V58">
         <v>23293</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W58" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2253000000000003</v>
+      </c>
+      <c r="X58" s="11">
+        <f t="shared" si="1"/>
+        <v>6.9821000000000009</v>
+      </c>
+      <c r="Y58" s="12">
+        <f t="shared" si="2"/>
+        <v>1.150000000000001E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>117</v>
       </c>
@@ -5042,8 +5762,20 @@
       <c r="V59">
         <v>12297</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W59" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.9129</v>
+      </c>
+      <c r="X59" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.5255000000000001</v>
+      </c>
+      <c r="Y59" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.13270000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>118</v>
       </c>
@@ -5110,8 +5842,20 @@
       <c r="V60">
         <v>19337</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W60" s="11">
+        <f t="shared" si="0"/>
+        <v>-3.1882999999999999</v>
+      </c>
+      <c r="X60" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.70480000000000054</v>
+      </c>
+      <c r="Y60" s="12">
+        <f t="shared" si="2"/>
+        <v>3.9300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>119</v>
       </c>
@@ -5178,8 +5922,20 @@
       <c r="V61">
         <v>16128</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W61" s="11">
+        <f t="shared" si="0"/>
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="X61" s="11">
+        <f t="shared" si="1"/>
+        <v>2.2919</v>
+      </c>
+      <c r="Y61" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.6299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>121</v>
       </c>
@@ -5246,8 +6002,20 @@
       <c r="V62">
         <v>18498</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W62" s="11">
+        <f t="shared" si="0"/>
+        <v>1.4951000000000003</v>
+      </c>
+      <c r="X62" s="11">
+        <f t="shared" si="1"/>
+        <v>1.0052999999999996</v>
+      </c>
+      <c r="Y62" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.36E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>122</v>
       </c>
@@ -5300,8 +6068,20 @@
       <c r="V63">
         <v>9059</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W63" s="11">
+        <f t="shared" si="0"/>
+        <v>-5.2683</v>
+      </c>
+      <c r="X63" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.98</v>
+      </c>
+      <c r="Y63" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.13730000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>124</v>
       </c>
@@ -5368,8 +6148,20 @@
       <c r="V64">
         <v>16233</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W64" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.45409999999999995</v>
+      </c>
+      <c r="X64" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.40960000000000019</v>
+      </c>
+      <c r="Y64" s="12">
+        <f t="shared" si="2"/>
+        <v>-0.1119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>125</v>
       </c>
@@ -5436,8 +6228,20 @@
       <c r="V65">
         <v>14374</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W65" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.11329999999999973</v>
+      </c>
+      <c r="X65" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.54939999999999989</v>
+      </c>
+      <c r="Y65" s="12">
+        <f t="shared" si="2"/>
+        <v>2.8900000000000009E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>126</v>
       </c>
@@ -5490,8 +6294,20 @@
       <c r="V66">
         <v>10547</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W66" s="11">
+        <f t="shared" si="0"/>
+        <v>-6.9545000000000003</v>
+      </c>
+      <c r="X66" s="11">
+        <f t="shared" si="1"/>
+        <v>-5.8</v>
+      </c>
+      <c r="Y66" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.5699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>127</v>
       </c>
@@ -5558,8 +6374,20 @@
       <c r="V67">
         <v>16207</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W67" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.22999999999999954</v>
+      </c>
+      <c r="X67" s="11">
+        <f t="shared" si="1"/>
+        <v>0.6897000000000002</v>
+      </c>
+      <c r="Y67" s="12">
+        <f t="shared" si="2"/>
+        <v>3.9999999999999897E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>128</v>
       </c>
@@ -5626,8 +6454,20 @@
       <c r="V68">
         <v>16507</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W68" s="11">
+        <f t="shared" ref="W68:W131" si="3">S68-R68</f>
+        <v>10.200399999999998</v>
+      </c>
+      <c r="X68" s="11">
+        <f t="shared" ref="X68:X131" si="4">U68-T68</f>
+        <v>2.7987000000000002</v>
+      </c>
+      <c r="Y68" s="12">
+        <f t="shared" ref="Y68:Y131" si="5">Q68-P68</f>
+        <v>-1.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>129</v>
       </c>
@@ -5694,8 +6534,20 @@
       <c r="V69">
         <v>19320</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W69" s="11">
+        <f t="shared" si="3"/>
+        <v>-0.89359999999999973</v>
+      </c>
+      <c r="X69" s="11">
+        <f t="shared" si="4"/>
+        <v>0.22330000000000005</v>
+      </c>
+      <c r="Y69" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.10540000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>130</v>
       </c>
@@ -5762,8 +6614,20 @@
       <c r="V70">
         <v>12763</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W70" s="11">
+        <f t="shared" si="3"/>
+        <v>1.0412999999999997</v>
+      </c>
+      <c r="X70" s="11">
+        <f t="shared" si="4"/>
+        <v>0.51089999999999947</v>
+      </c>
+      <c r="Y70" s="12">
+        <f t="shared" si="5"/>
+        <v>-3.3099999999999991E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>131</v>
       </c>
@@ -5830,8 +6694,20 @@
       <c r="V71">
         <v>19574</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W71" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.8973999999999998</v>
+      </c>
+      <c r="X71" s="11">
+        <f t="shared" si="4"/>
+        <v>8.1799999999999873E-2</v>
+      </c>
+      <c r="Y71" s="12">
+        <f t="shared" si="5"/>
+        <v>-8.3000000000000018E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>133</v>
       </c>
@@ -5884,8 +6760,20 @@
       <c r="V72">
         <v>14696</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W72" s="11">
+        <f t="shared" si="3"/>
+        <v>-2.9043999999999999</v>
+      </c>
+      <c r="X72" s="11">
+        <f t="shared" si="4"/>
+        <v>-3.2898000000000001</v>
+      </c>
+      <c r="Y72" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.2082</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>55</v>
       </c>
@@ -5952,8 +6840,20 @@
       <c r="V73">
         <v>19716</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W73" s="11">
+        <f t="shared" si="3"/>
+        <v>0.36830000000000007</v>
+      </c>
+      <c r="X73" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.29010000000000025</v>
+      </c>
+      <c r="Y73" s="12">
+        <f t="shared" si="5"/>
+        <v>-4.5600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>134</v>
       </c>
@@ -6020,8 +6920,20 @@
       <c r="V74">
         <v>16727</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W74" s="11">
+        <f t="shared" si="3"/>
+        <v>-6.0231000000000003</v>
+      </c>
+      <c r="X74" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.9083000000000006</v>
+      </c>
+      <c r="Y74" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1525</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>135</v>
       </c>
@@ -6074,8 +6986,20 @@
       <c r="V75">
         <v>19942</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W75" s="11">
+        <f t="shared" si="3"/>
+        <v>-5.1702000000000004</v>
+      </c>
+      <c r="X75" s="11">
+        <f t="shared" si="4"/>
+        <v>-5.74</v>
+      </c>
+      <c r="Y75" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>136</v>
       </c>
@@ -6128,8 +7052,20 @@
       <c r="V76">
         <v>2882</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W76" s="11">
+        <f t="shared" si="3"/>
+        <v>-4.3074000000000003</v>
+      </c>
+      <c r="X76" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.0667</v>
+      </c>
+      <c r="Y76" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1406</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>137</v>
       </c>
@@ -6196,8 +7132,20 @@
       <c r="V77">
         <v>20039</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W77" s="11">
+        <f t="shared" si="3"/>
+        <v>-2.6280000000000001</v>
+      </c>
+      <c r="X77" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.9908999999999999</v>
+      </c>
+      <c r="Y77" s="12">
+        <f t="shared" si="5"/>
+        <v>-6.5599999999999992E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>138</v>
       </c>
@@ -6264,8 +7212,20 @@
       <c r="V78">
         <v>11828</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W78" s="11">
+        <f t="shared" si="3"/>
+        <v>0.48070000000000013</v>
+      </c>
+      <c r="X78" s="11">
+        <f t="shared" si="4"/>
+        <v>1.1498000000000004</v>
+      </c>
+      <c r="Y78" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>139</v>
       </c>
@@ -6332,8 +7292,20 @@
       <c r="V79">
         <v>17464</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W79" s="11">
+        <f t="shared" si="3"/>
+        <v>1.3007999999999997</v>
+      </c>
+      <c r="X79" s="11">
+        <f t="shared" si="4"/>
+        <v>0.60179999999999989</v>
+      </c>
+      <c r="Y79" s="12">
+        <f t="shared" si="5"/>
+        <v>-5.7800000000000004E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>140</v>
       </c>
@@ -6400,8 +7372,20 @@
       <c r="V80">
         <v>20100</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W80" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.6699000000000002</v>
+      </c>
+      <c r="X80" s="11">
+        <f t="shared" si="4"/>
+        <v>-2.8585000000000003</v>
+      </c>
+      <c r="Y80" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1623</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>141</v>
       </c>
@@ -6468,8 +7452,20 @@
       <c r="V81">
         <v>14524</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W81" s="11">
+        <f t="shared" si="3"/>
+        <v>0.27619999999999978</v>
+      </c>
+      <c r="X81" s="11">
+        <f t="shared" si="4"/>
+        <v>0.77340000000000009</v>
+      </c>
+      <c r="Y81" s="12">
+        <f t="shared" si="5"/>
+        <v>-4.99E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>142</v>
       </c>
@@ -6536,8 +7532,20 @@
       <c r="V82">
         <v>20023</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W82" s="11">
+        <f t="shared" si="3"/>
+        <v>9.5000000000000639E-3</v>
+      </c>
+      <c r="X82" s="11">
+        <f t="shared" si="4"/>
+        <v>0.96819999999999951</v>
+      </c>
+      <c r="Y82" s="12">
+        <f t="shared" si="5"/>
+        <v>3.1600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>144</v>
       </c>
@@ -6604,8 +7612,20 @@
       <c r="V83">
         <v>12673</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W83" s="11">
+        <f t="shared" si="3"/>
+        <v>0.2246999999999999</v>
+      </c>
+      <c r="X83" s="11">
+        <f t="shared" si="4"/>
+        <v>0.35489999999999977</v>
+      </c>
+      <c r="Y83" s="12">
+        <f t="shared" si="5"/>
+        <v>-1.9400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>145</v>
       </c>
@@ -6672,8 +7692,20 @@
       <c r="V84">
         <v>9073</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W84" s="11">
+        <f t="shared" si="3"/>
+        <v>0.33300000000000018</v>
+      </c>
+      <c r="X84" s="11">
+        <f t="shared" si="4"/>
+        <v>1.7092999999999998</v>
+      </c>
+      <c r="Y84" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>146</v>
       </c>
@@ -6726,8 +7758,20 @@
       <c r="V85">
         <v>20344</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W85" s="11">
+        <f t="shared" si="3"/>
+        <v>-4.5</v>
+      </c>
+      <c r="X85" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.94</v>
+      </c>
+      <c r="Y85" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>147</v>
       </c>
@@ -6794,8 +7838,20 @@
       <c r="V86">
         <v>15690</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W86" s="11">
+        <f t="shared" si="3"/>
+        <v>-0.69709999999999983</v>
+      </c>
+      <c r="X86" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.2585000000000002</v>
+      </c>
+      <c r="Y86" s="12">
+        <f t="shared" si="5"/>
+        <v>9.1099999999999987E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>148</v>
       </c>
@@ -6862,8 +7918,20 @@
       <c r="V87">
         <v>16306</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W87" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.2963000000000005</v>
+      </c>
+      <c r="X87" s="11">
+        <f t="shared" si="4"/>
+        <v>3.444</v>
+      </c>
+      <c r="Y87" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.23080000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>149</v>
       </c>
@@ -6930,8 +7998,20 @@
       <c r="V88">
         <v>17169</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W88" s="11">
+        <f t="shared" si="3"/>
+        <v>30.519200000000001</v>
+      </c>
+      <c r="X88" s="11">
+        <f t="shared" si="4"/>
+        <v>7.9465000000000003</v>
+      </c>
+      <c r="Y88" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.44799999999999995</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>150</v>
       </c>
@@ -6984,8 +8064,20 @@
       <c r="V89">
         <v>19582</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W89" s="11">
+        <f t="shared" si="3"/>
+        <v>-2.4544999999999999</v>
+      </c>
+      <c r="X89" s="11">
+        <f t="shared" si="4"/>
+        <v>-5.51</v>
+      </c>
+      <c r="Y89" s="12">
+        <f t="shared" si="5"/>
+        <v>-3.3300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>151</v>
       </c>
@@ -7038,8 +8130,20 @@
       <c r="V90">
         <v>17030</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W90" s="11">
+        <f t="shared" si="3"/>
+        <v>-5.9668999999999999</v>
+      </c>
+      <c r="X90" s="11">
+        <f t="shared" si="4"/>
+        <v>-5.0803000000000003</v>
+      </c>
+      <c r="Y90" s="12">
+        <f t="shared" si="5"/>
+        <v>-6.3500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>153</v>
       </c>
@@ -7106,8 +8210,20 @@
       <c r="V91">
         <v>12808</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W91" s="11">
+        <f t="shared" si="3"/>
+        <v>1.0745999999999998</v>
+      </c>
+      <c r="X91" s="11">
+        <f t="shared" si="4"/>
+        <v>1.2812999999999999</v>
+      </c>
+      <c r="Y91" s="12">
+        <f t="shared" si="5"/>
+        <v>-7.0800000000000016E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>154</v>
       </c>
@@ -7148,8 +8264,20 @@
       <c r="V92">
         <v>17581</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W92" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X92" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y92" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>156</v>
       </c>
@@ -7216,8 +8344,20 @@
       <c r="V93">
         <v>16074</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W93" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.8000000000000007</v>
+      </c>
+      <c r="X93" s="11">
+        <f t="shared" si="4"/>
+        <v>8.2699999999999996E-2</v>
+      </c>
+      <c r="Y93" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.21330000000000005</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>157</v>
       </c>
@@ -7270,8 +8410,20 @@
       <c r="V94">
         <v>18135</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W94" s="11">
+        <f t="shared" si="3"/>
+        <v>-8.1818000000000008</v>
+      </c>
+      <c r="X94" s="11">
+        <f t="shared" si="4"/>
+        <v>-7.0503999999999998</v>
+      </c>
+      <c r="Y94" s="12">
+        <f t="shared" si="5"/>
+        <v>-7.5899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>158</v>
       </c>
@@ -7338,8 +8490,20 @@
       <c r="V95">
         <v>14682</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W95" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.0771000000000002</v>
+      </c>
+      <c r="X95" s="11">
+        <f t="shared" si="4"/>
+        <v>0.62779999999999969</v>
+      </c>
+      <c r="Y95" s="12">
+        <f t="shared" si="5"/>
+        <v>6.6999999999999976E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>159</v>
       </c>
@@ -7406,8 +8570,20 @@
       <c r="V96">
         <v>8700</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W96" s="11">
+        <f t="shared" si="3"/>
+        <v>-0.35890000000000022</v>
+      </c>
+      <c r="X96" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.14500000000000002</v>
+      </c>
+      <c r="Y96" s="12">
+        <f t="shared" si="5"/>
+        <v>-6.9199999999999984E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>160</v>
       </c>
@@ -7474,8 +8650,20 @@
       <c r="V97">
         <v>12910</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W97" s="11">
+        <f t="shared" si="3"/>
+        <v>-2.8734999999999999</v>
+      </c>
+      <c r="X97" s="11">
+        <f t="shared" si="4"/>
+        <v>0.5490999999999997</v>
+      </c>
+      <c r="Y97" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.14980000000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>161</v>
       </c>
@@ -7542,8 +8730,20 @@
       <c r="V98">
         <v>19206</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W98" s="11">
+        <f t="shared" si="3"/>
+        <v>1.2932000000000001</v>
+      </c>
+      <c r="X98" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.26039999999999974</v>
+      </c>
+      <c r="Y98" s="12">
+        <f t="shared" si="5"/>
+        <v>-2.4799999999999996E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>162</v>
       </c>
@@ -7610,8 +8810,20 @@
       <c r="V99">
         <v>19349</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W99" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.2896000000000005</v>
+      </c>
+      <c r="X99" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.1750000000000003</v>
+      </c>
+      <c r="Y99" s="12">
+        <f t="shared" si="5"/>
+        <v>-1.9699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>163</v>
       </c>
@@ -7678,8 +8890,20 @@
       <c r="V100">
         <v>10688</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W100" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.2233000000000005</v>
+      </c>
+      <c r="X100" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.5444000000000004</v>
+      </c>
+      <c r="Y100" s="12">
+        <f t="shared" si="5"/>
+        <v>-8.4699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>164</v>
       </c>
@@ -7746,8 +8970,20 @@
       <c r="V101">
         <v>17192</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W101" s="11">
+        <f t="shared" si="3"/>
+        <v>-0.60970000000000013</v>
+      </c>
+      <c r="X101" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.85999999999999988</v>
+      </c>
+      <c r="Y101" s="12">
+        <f t="shared" si="5"/>
+        <v>6.989999999999999E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>165</v>
       </c>
@@ -7814,8 +9050,20 @@
       <c r="V102">
         <v>13528</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W102" s="11">
+        <f t="shared" si="3"/>
+        <v>4.6452</v>
+      </c>
+      <c r="X102" s="11">
+        <f t="shared" si="4"/>
+        <v>2.633</v>
+      </c>
+      <c r="Y102" s="12">
+        <f t="shared" si="5"/>
+        <v>-6.1600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>166</v>
       </c>
@@ -7882,8 +9130,20 @@
       <c r="V103">
         <v>16401</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W103" s="11">
+        <f t="shared" si="3"/>
+        <v>1.2760999999999996</v>
+      </c>
+      <c r="X103" s="11">
+        <f t="shared" si="4"/>
+        <v>1.1219000000000001</v>
+      </c>
+      <c r="Y103" s="12">
+        <f t="shared" si="5"/>
+        <v>-7.3000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>167</v>
       </c>
@@ -7936,8 +9196,20 @@
       <c r="V104">
         <v>6832</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W104" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.3650000000000002</v>
+      </c>
+      <c r="X104" s="11">
+        <f t="shared" si="4"/>
+        <v>-3.6501999999999999</v>
+      </c>
+      <c r="Y104" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>168</v>
       </c>
@@ -7992,8 +9264,20 @@
       <c r="V105">
         <v>16432</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W105" s="11">
+        <f t="shared" si="3"/>
+        <v>8.5263000000000009</v>
+      </c>
+      <c r="X105" s="11">
+        <f t="shared" si="4"/>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="Y105" s="12">
+        <f t="shared" si="5"/>
+        <v>-3.1199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>169</v>
       </c>
@@ -8060,8 +9344,20 @@
       <c r="V106">
         <v>11384</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W106" s="11">
+        <f t="shared" si="3"/>
+        <v>-0.96519999999999984</v>
+      </c>
+      <c r="X106" s="11">
+        <f t="shared" si="4"/>
+        <v>1.2392000000000003</v>
+      </c>
+      <c r="Y106" s="12">
+        <f t="shared" si="5"/>
+        <v>-7.5500000000000012E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>170</v>
       </c>
@@ -8128,8 +9424,20 @@
       <c r="V107">
         <v>19249</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W107" s="11">
+        <f t="shared" si="3"/>
+        <v>8.680000000000021E-2</v>
+      </c>
+      <c r="X107" s="11">
+        <f t="shared" si="4"/>
+        <v>0.72989999999999977</v>
+      </c>
+      <c r="Y107" s="12">
+        <f t="shared" si="5"/>
+        <v>-5.0199999999999995E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>171</v>
       </c>
@@ -8196,8 +9504,20 @@
       <c r="V108">
         <v>19403</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W108" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.6109999999999998</v>
+      </c>
+      <c r="X108" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.15010000000000012</v>
+      </c>
+      <c r="Y108" s="12">
+        <f t="shared" si="5"/>
+        <v>-9.5100000000000018E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>172</v>
       </c>
@@ -8252,8 +9572,20 @@
       <c r="V109">
         <v>16201</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W109" s="11">
+        <f t="shared" si="3"/>
+        <v>-4.7492000000000001</v>
+      </c>
+      <c r="X109" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.1055999999999999</v>
+      </c>
+      <c r="Y109" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1201</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>173</v>
       </c>
@@ -8320,8 +9652,20 @@
       <c r="V110">
         <v>17969</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W110" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.5440000000000005</v>
+      </c>
+      <c r="X110" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.38859999999999939</v>
+      </c>
+      <c r="Y110" s="12">
+        <f t="shared" si="5"/>
+        <v>5.8599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>174</v>
       </c>
@@ -8388,8 +9732,20 @@
       <c r="V111">
         <v>17793</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W111" s="11">
+        <f t="shared" si="3"/>
+        <v>0.68060000000000009</v>
+      </c>
+      <c r="X111" s="11">
+        <f t="shared" si="4"/>
+        <v>0.17090000000000005</v>
+      </c>
+      <c r="Y111" s="12">
+        <f t="shared" si="5"/>
+        <v>-3.2999999999999974E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>175</v>
       </c>
@@ -8456,8 +9812,20 @@
       <c r="V112">
         <v>14361</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W112" s="11">
+        <f t="shared" si="3"/>
+        <v>0.45690000000000008</v>
+      </c>
+      <c r="X112" s="11">
+        <f t="shared" si="4"/>
+        <v>0.52869999999999973</v>
+      </c>
+      <c r="Y112" s="12">
+        <f t="shared" si="5"/>
+        <v>3.0799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>176</v>
       </c>
@@ -8524,8 +9892,20 @@
       <c r="V113">
         <v>12777</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W113" s="11">
+        <f t="shared" si="3"/>
+        <v>0.68909999999999982</v>
+      </c>
+      <c r="X113" s="11">
+        <f t="shared" si="4"/>
+        <v>0.30089999999999995</v>
+      </c>
+      <c r="Y113" s="12">
+        <f t="shared" si="5"/>
+        <v>-3.7099999999999994E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>177</v>
       </c>
@@ -8592,8 +9972,20 @@
       <c r="V114">
         <v>10603</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W114" s="11">
+        <f t="shared" si="3"/>
+        <v>0.85110000000000019</v>
+      </c>
+      <c r="X114" s="11">
+        <f t="shared" si="4"/>
+        <v>1.1432000000000002</v>
+      </c>
+      <c r="Y114" s="12">
+        <f t="shared" si="5"/>
+        <v>-9.0799999999999992E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>179</v>
       </c>
@@ -8660,8 +10052,20 @@
       <c r="V115">
         <v>11762</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W115" s="11">
+        <f t="shared" si="3"/>
+        <v>1.3204000000000002</v>
+      </c>
+      <c r="X115" s="11">
+        <f t="shared" si="4"/>
+        <v>1.7013000000000003</v>
+      </c>
+      <c r="Y115" s="12">
+        <f t="shared" si="5"/>
+        <v>-8.09E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>180</v>
       </c>
@@ -8728,8 +10132,20 @@
       <c r="V116">
         <v>6499</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W116" s="11">
+        <f t="shared" si="3"/>
+        <v>13.710799999999999</v>
+      </c>
+      <c r="X116" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.56120000000000037</v>
+      </c>
+      <c r="Y116" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1089</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>181</v>
       </c>
@@ -8796,8 +10212,20 @@
       <c r="V117">
         <v>20373</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W117" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.2443999999999997</v>
+      </c>
+      <c r="X117" s="11">
+        <f t="shared" si="4"/>
+        <v>-0.80649999999999977</v>
+      </c>
+      <c r="Y117" s="12">
+        <f t="shared" si="5"/>
+        <v>7.4100000000000027E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>182</v>
       </c>
@@ -8864,8 +10292,20 @@
       <c r="V118">
         <v>16981</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W118" s="11">
+        <f t="shared" si="3"/>
+        <v>0.21649999999999991</v>
+      </c>
+      <c r="X118" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.2200000000000237E-2</v>
+      </c>
+      <c r="Y118" s="12">
+        <f t="shared" si="5"/>
+        <v>-7.9600000000000004E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>183</v>
       </c>
@@ -8932,8 +10372,20 @@
       <c r="V119">
         <v>15890</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W119" s="11">
+        <f t="shared" si="3"/>
+        <v>1.5209000000000001</v>
+      </c>
+      <c r="X119" s="11">
+        <f t="shared" si="4"/>
+        <v>1.7491000000000003</v>
+      </c>
+      <c r="Y119" s="12">
+        <f t="shared" si="5"/>
+        <v>-6.7099999999999993E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>184</v>
       </c>
@@ -8986,8 +10438,20 @@
       <c r="V120">
         <v>8185</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W120" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.6871</v>
+      </c>
+      <c r="X120" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.3221999999999996</v>
+      </c>
+      <c r="Y120" s="12">
+        <f t="shared" si="5"/>
+        <v>-9.4700000000000006E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>185</v>
       </c>
@@ -9054,8 +10518,20 @@
       <c r="V121">
         <v>13483</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W121" s="11">
+        <f t="shared" si="3"/>
+        <v>8.0357000000000003</v>
+      </c>
+      <c r="X121" s="11">
+        <f t="shared" si="4"/>
+        <v>5.93</v>
+      </c>
+      <c r="Y121" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1658</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>186</v>
       </c>
@@ -9122,8 +10598,20 @@
       <c r="V122">
         <v>15042</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W122" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.1675999999999997</v>
+      </c>
+      <c r="X122" s="11">
+        <f t="shared" si="4"/>
+        <v>0.27870000000000017</v>
+      </c>
+      <c r="Y122" s="12">
+        <f t="shared" si="5"/>
+        <v>-2.1900000000000003E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>187</v>
       </c>
@@ -9176,8 +10664,20 @@
       <c r="V123">
         <v>9029</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W123" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.4588999999999999</v>
+      </c>
+      <c r="X123" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.0766999999999998</v>
+      </c>
+      <c r="Y123" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>188</v>
       </c>
@@ -9244,8 +10744,20 @@
       <c r="V124">
         <v>8241</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W124" s="11">
+        <f t="shared" si="3"/>
+        <v>-9.4599999999999795E-2</v>
+      </c>
+      <c r="X124" s="11">
+        <f t="shared" si="4"/>
+        <v>0.57089999999999996</v>
+      </c>
+      <c r="Y124" s="12">
+        <f t="shared" si="5"/>
+        <v>-4.0099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>189</v>
       </c>
@@ -9298,8 +10810,20 @@
       <c r="V125">
         <v>12452</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W125" s="11">
+        <f t="shared" si="3"/>
+        <v>-3.7099000000000002</v>
+      </c>
+      <c r="X125" s="11">
+        <f t="shared" si="4"/>
+        <v>-4.5582000000000003</v>
+      </c>
+      <c r="Y125" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.1016</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>190</v>
       </c>
@@ -9366,8 +10890,20 @@
       <c r="V126">
         <v>11674</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W126" s="11">
+        <f t="shared" si="3"/>
+        <v>0.45279999999999987</v>
+      </c>
+      <c r="X126" s="11">
+        <f t="shared" si="4"/>
+        <v>0.63300000000000045</v>
+      </c>
+      <c r="Y126" s="12">
+        <f t="shared" si="5"/>
+        <v>5.0999999999999934E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>191</v>
       </c>
@@ -9434,8 +10970,20 @@
       <c r="V127">
         <v>18510</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W127" s="11">
+        <f t="shared" si="3"/>
+        <v>-4.4211999999999998</v>
+      </c>
+      <c r="X127" s="11">
+        <f t="shared" si="4"/>
+        <v>0.43059999999999921</v>
+      </c>
+      <c r="Y127" s="12">
+        <f t="shared" si="5"/>
+        <v>1.6199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>192</v>
       </c>
@@ -9502,8 +11050,20 @@
       <c r="V128">
         <v>19618</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W128" s="11">
+        <f t="shared" si="3"/>
+        <v>1.3283000000000005</v>
+      </c>
+      <c r="X128" s="11">
+        <f t="shared" si="4"/>
+        <v>0.42999999999999972</v>
+      </c>
+      <c r="Y128" s="12">
+        <f t="shared" si="5"/>
+        <v>1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>193</v>
       </c>
@@ -9570,8 +11130,20 @@
       <c r="V129">
         <v>17536</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W129" s="11">
+        <f t="shared" si="3"/>
+        <v>-4.2949999999999999</v>
+      </c>
+      <c r="X129" s="11">
+        <f t="shared" si="4"/>
+        <v>-3.3107000000000006</v>
+      </c>
+      <c r="Y129" s="12">
+        <f t="shared" si="5"/>
+        <v>7.8899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>194</v>
       </c>
@@ -9638,8 +11210,20 @@
       <c r="V130">
         <v>16137</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W130" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.3080000000000003</v>
+      </c>
+      <c r="X130" s="11">
+        <f t="shared" si="4"/>
+        <v>-1.9819999999999998</v>
+      </c>
+      <c r="Y130" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1361</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>195</v>
       </c>
@@ -9706,8 +11290,20 @@
       <c r="V131">
         <v>15010</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W131" s="11">
+        <f t="shared" si="3"/>
+        <v>0.58639999999999981</v>
+      </c>
+      <c r="X131" s="11">
+        <f t="shared" si="4"/>
+        <v>1.4229000000000003</v>
+      </c>
+      <c r="Y131" s="12">
+        <f t="shared" si="5"/>
+        <v>-0.14219999999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>196</v>
       </c>
@@ -9774,8 +11370,20 @@
       <c r="V132">
         <v>13218</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W132" s="11">
+        <f t="shared" ref="W132:W159" si="6">S132-R132</f>
+        <v>0.32739999999999947</v>
+      </c>
+      <c r="X132" s="11">
+        <f t="shared" ref="X132:X159" si="7">U132-T132</f>
+        <v>0.14829999999999988</v>
+      </c>
+      <c r="Y132" s="12">
+        <f t="shared" ref="Y132:Y159" si="8">Q132-P132</f>
+        <v>1.1399999999999993E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>197</v>
       </c>
@@ -9842,8 +11450,20 @@
       <c r="V133">
         <v>15051</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W133" s="11">
+        <f t="shared" si="6"/>
+        <v>3.2496999999999998</v>
+      </c>
+      <c r="X133" s="11">
+        <f t="shared" si="7"/>
+        <v>4.7633000000000001</v>
+      </c>
+      <c r="Y133" s="12">
+        <f t="shared" si="8"/>
+        <v>3.3599999999999991E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>198</v>
       </c>
@@ -9910,8 +11530,20 @@
       <c r="V134">
         <v>17755</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W134" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.38729999999999976</v>
+      </c>
+      <c r="X134" s="11">
+        <f t="shared" si="7"/>
+        <v>0.93389999999999951</v>
+      </c>
+      <c r="Y134" s="12">
+        <f t="shared" si="8"/>
+        <v>7.8499999999999986E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -9978,8 +11610,20 @@
       <c r="V135">
         <v>15551</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W135" s="11">
+        <f t="shared" si="6"/>
+        <v>-1.5362</v>
+      </c>
+      <c r="X135" s="11">
+        <f t="shared" si="7"/>
+        <v>-1.2245999999999997</v>
+      </c>
+      <c r="Y135" s="12">
+        <f t="shared" si="8"/>
+        <v>4.859999999999999E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>200</v>
       </c>
@@ -10046,8 +11690,20 @@
       <c r="V136">
         <v>14120</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W136" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.24199999999999999</v>
+      </c>
+      <c r="X136" s="11">
+        <f t="shared" si="7"/>
+        <v>0.42870000000000008</v>
+      </c>
+      <c r="Y136" s="12">
+        <f t="shared" si="8"/>
+        <v>-1.3499999999999984E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>201</v>
       </c>
@@ -10114,8 +11770,20 @@
       <c r="V137">
         <v>17355</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W137" s="11">
+        <f t="shared" si="6"/>
+        <v>8.5900000000000087E-2</v>
+      </c>
+      <c r="X137" s="11">
+        <f t="shared" si="7"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="Y137" s="12">
+        <f t="shared" si="8"/>
+        <v>2.1199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>202</v>
       </c>
@@ -10156,8 +11824,20 @@
       <c r="V138">
         <v>17126</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W138" s="11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X138" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y138" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>34</v>
       </c>
@@ -10212,8 +11892,20 @@
       <c r="V139">
         <v>19755</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W139" s="11">
+        <f t="shared" si="6"/>
+        <v>3.6135999999999999</v>
+      </c>
+      <c r="X139" s="11">
+        <f t="shared" si="7"/>
+        <v>3.6522000000000001</v>
+      </c>
+      <c r="Y139" s="12">
+        <f t="shared" si="8"/>
+        <v>0.19489999999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>203</v>
       </c>
@@ -10280,8 +11972,20 @@
       <c r="V140">
         <v>14975</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W140" s="11">
+        <f t="shared" si="6"/>
+        <v>0.3158000000000003</v>
+      </c>
+      <c r="X140" s="11">
+        <f t="shared" si="7"/>
+        <v>1.2221000000000002</v>
+      </c>
+      <c r="Y140" s="12">
+        <f t="shared" si="8"/>
+        <v>-1.5299999999999994E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>204</v>
       </c>
@@ -10336,8 +12040,20 @@
       <c r="V141">
         <v>17282</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W141" s="11">
+        <f t="shared" si="6"/>
+        <v>3.5047999999999999</v>
+      </c>
+      <c r="X141" s="11">
+        <f t="shared" si="7"/>
+        <v>2.97</v>
+      </c>
+      <c r="Y141" s="12">
+        <f t="shared" si="8"/>
+        <v>0.2772</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>205</v>
       </c>
@@ -10404,8 +12120,20 @@
       <c r="V142">
         <v>16731</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W142" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.69679999999999964</v>
+      </c>
+      <c r="X142" s="11">
+        <f t="shared" si="7"/>
+        <v>-3.33</v>
+      </c>
+      <c r="Y142" s="12">
+        <f t="shared" si="8"/>
+        <v>0.1837</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>206</v>
       </c>
@@ -10472,8 +12200,20 @@
       <c r="V143">
         <v>6893</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W143" s="11">
+        <f t="shared" si="6"/>
+        <v>1.1265000000000005</v>
+      </c>
+      <c r="X143" s="11">
+        <f t="shared" si="7"/>
+        <v>0.82270000000000021</v>
+      </c>
+      <c r="Y143" s="12">
+        <f t="shared" si="8"/>
+        <v>-3.0499999999999985E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>207</v>
       </c>
@@ -10526,8 +12266,20 @@
       <c r="V144">
         <v>16164</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W144" s="11">
+        <f t="shared" si="6"/>
+        <v>-6.1094999999999997</v>
+      </c>
+      <c r="X144" s="11">
+        <f t="shared" si="7"/>
+        <v>-5.59</v>
+      </c>
+      <c r="Y144" s="12">
+        <f t="shared" si="8"/>
+        <v>-9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>208</v>
       </c>
@@ -10594,8 +12346,20 @@
       <c r="V145">
         <v>13942</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W145" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.69679999999999964</v>
+      </c>
+      <c r="X145" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.42490000000000006</v>
+      </c>
+      <c r="Y145" s="12">
+        <f t="shared" si="8"/>
+        <v>6.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>209</v>
       </c>
@@ -10662,8 +12426,20 @@
       <c r="V146">
         <v>9784</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W146" s="11">
+        <f t="shared" si="6"/>
+        <v>1.4676000000000005</v>
+      </c>
+      <c r="X146" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0056000000000003</v>
+      </c>
+      <c r="Y146" s="12">
+        <f t="shared" si="8"/>
+        <v>-2.18E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>210</v>
       </c>
@@ -10716,8 +12492,20 @@
       <c r="V147">
         <v>8493</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W147" s="11">
+        <f t="shared" si="6"/>
+        <v>-6.1670999999999996</v>
+      </c>
+      <c r="X147" s="11">
+        <f t="shared" si="7"/>
+        <v>-4.9203999999999999</v>
+      </c>
+      <c r="Y147" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.1227</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>211</v>
       </c>
@@ -10770,8 +12558,20 @@
       <c r="V148">
         <v>11012</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W148" s="11">
+        <f t="shared" si="6"/>
+        <v>-4.6957000000000004</v>
+      </c>
+      <c r="X148" s="11">
+        <f t="shared" si="7"/>
+        <v>-4.79</v>
+      </c>
+      <c r="Y148" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.1852</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>212</v>
       </c>
@@ -10838,8 +12638,20 @@
       <c r="V149">
         <v>16511</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W149" s="11">
+        <f t="shared" si="6"/>
+        <v>0.28199999999999958</v>
+      </c>
+      <c r="X149" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.33620000000000028</v>
+      </c>
+      <c r="Y149" s="12">
+        <f t="shared" si="8"/>
+        <v>3.3099999999999991E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>213</v>
       </c>
@@ -10892,8 +12704,20 @@
       <c r="V150">
         <v>1345</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W150" s="11">
+        <f t="shared" si="6"/>
+        <v>-4.7085999999999997</v>
+      </c>
+      <c r="X150" s="11">
+        <f t="shared" si="7"/>
+        <v>-3.8984999999999999</v>
+      </c>
+      <c r="Y150" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.14199999999999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>214</v>
       </c>
@@ -10960,8 +12784,20 @@
       <c r="V151">
         <v>15264</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W151" s="11">
+        <f t="shared" si="6"/>
+        <v>0.58370000000000033</v>
+      </c>
+      <c r="X151" s="11">
+        <f t="shared" si="7"/>
+        <v>0.22039999999999971</v>
+      </c>
+      <c r="Y151" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.1431</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>215</v>
       </c>
@@ -11028,8 +12864,20 @@
       <c r="V152">
         <v>11836</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W152" s="11">
+        <f t="shared" si="6"/>
+        <v>-8.9000000000000412E-2</v>
+      </c>
+      <c r="X152" s="11">
+        <f t="shared" si="7"/>
+        <v>0.2240000000000002</v>
+      </c>
+      <c r="Y152" s="12">
+        <f t="shared" si="8"/>
+        <v>-5.3999999999999881E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>216</v>
       </c>
@@ -11096,8 +12944,20 @@
       <c r="V153">
         <v>17186</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W153" s="11">
+        <f t="shared" si="6"/>
+        <v>-1.137</v>
+      </c>
+      <c r="X153" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.95459999999999967</v>
+      </c>
+      <c r="Y153" s="12">
+        <f t="shared" si="8"/>
+        <v>5.6599999999999984E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>217</v>
       </c>
@@ -11164,8 +13024,20 @@
       <c r="V154">
         <v>8302</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W154" s="11">
+        <f t="shared" si="6"/>
+        <v>0.17419999999999991</v>
+      </c>
+      <c r="X154" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.11439999999999984</v>
+      </c>
+      <c r="Y154" s="12">
+        <f t="shared" si="8"/>
+        <v>-4.1999999999999954E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>219</v>
       </c>
@@ -11232,8 +13104,20 @@
       <c r="V155">
         <v>15100</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W155" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.97500000000000009</v>
+      </c>
+      <c r="X155" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.20080000000000009</v>
+      </c>
+      <c r="Y155" s="12">
+        <f t="shared" si="8"/>
+        <v>0.12159999999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>220</v>
       </c>
@@ -11300,8 +13184,20 @@
       <c r="V156">
         <v>12760</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W156" s="11">
+        <f t="shared" si="6"/>
+        <v>-0.99580000000000002</v>
+      </c>
+      <c r="X156" s="11">
+        <f t="shared" si="7"/>
+        <v>-0.63819999999999988</v>
+      </c>
+      <c r="Y156" s="12">
+        <f t="shared" si="8"/>
+        <v>7.7799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>221</v>
       </c>
@@ -11368,8 +13264,20 @@
       <c r="V157">
         <v>6316</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W157" s="11">
+        <f t="shared" si="6"/>
+        <v>0.49160000000000004</v>
+      </c>
+      <c r="X157" s="11">
+        <f t="shared" si="7"/>
+        <v>0.90340000000000042</v>
+      </c>
+      <c r="Y157" s="12">
+        <f t="shared" si="8"/>
+        <v>5.8900000000000008E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>222</v>
       </c>
@@ -11436,8 +13344,20 @@
       <c r="V158">
         <v>13654</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W158" s="11">
+        <f t="shared" si="6"/>
+        <v>-1.4235999999999995</v>
+      </c>
+      <c r="X158" s="11">
+        <f t="shared" si="7"/>
+        <v>-1.6042999999999998</v>
+      </c>
+      <c r="Y158" s="12">
+        <f t="shared" si="8"/>
+        <v>4.7999999999999987E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>224</v>
       </c>
@@ -11503,6 +13423,18 @@
       </c>
       <c r="V159">
         <v>5530</v>
+      </c>
+      <c r="W159" s="11">
+        <f t="shared" si="6"/>
+        <v>-6.2228999999999992</v>
+      </c>
+      <c r="X159" s="11">
+        <f t="shared" si="7"/>
+        <v>-3.1799999999999997</v>
+      </c>
+      <c r="Y159" s="12">
+        <f t="shared" si="8"/>
+        <v>4.1599999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/TJ_Surgery_2018_2023_Pitchers_FILLED.xlsx
+++ b/TJ_Surgery_2018_2023_Pitchers_FILLED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6772c73964c7b6d/TJPROJECT599/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_213335CB1137CA1B1EF52B8EAEA92375D8FA6F64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41BDC118-5871-4149-9427-87CD73D12982}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_213335CBACE7C9BCD9E2EBC4E26D0F35D8FA7C81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299CA8CA-2E84-48C0-A81C-7706645655C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="246">
   <si>
     <t>Player</t>
   </si>
@@ -183,6 +183,9 @@
     <t>SD</t>
   </si>
   <si>
+    <t>NULL</t>
+  </si>
+  <si>
     <t>Antonio Senzatela</t>
   </si>
   <si>
@@ -759,13 +762,16 @@
     <t>No seasons found for [2015, 2016, 2017]</t>
   </si>
   <si>
-    <t>K-BB% Diff.(+ improvement)</t>
-  </si>
-  <si>
-    <t>FIP Diff. (- improvement)</t>
-  </si>
-  <si>
-    <t>ERA Diff. (- improvement)</t>
+    <t>Diff in ERA(- improvement)</t>
+  </si>
+  <si>
+    <t>Diff in FIP(- improvement)</t>
+  </si>
+  <si>
+    <t>Diff in K-BB%(+ improvement)</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
   </si>
 </sst>
 </file>
@@ -776,7 +782,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,6 +799,14 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -821,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,9 +850,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,6 +869,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1141,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y159"/>
+  <dimension ref="A1:Y160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1162,9 +1181,9 @@
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="23" max="23" width="13.6328125" customWidth="1"/>
-    <col min="24" max="24" width="13.26953125" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="23" max="23" width="13.1796875" customWidth="1"/>
+    <col min="24" max="24" width="12.6328125" customWidth="1"/>
+    <col min="25" max="25" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="26" x14ac:dyDescent="0.35">
@@ -1235,13 +1254,13 @@
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="Y1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
@@ -1392,15 +1411,15 @@
         <v>20666</v>
       </c>
       <c r="W3" s="11">
-        <f>S3-R3</f>
+        <f t="shared" ref="W3:W66" si="0">S3-R3</f>
         <v>1.0273000000000003</v>
       </c>
       <c r="X3" s="11">
-        <f>U3-T3</f>
+        <f t="shared" ref="X3:X66" si="1">U3-T3</f>
         <v>0.72279999999999989</v>
       </c>
       <c r="Y3" s="12">
-        <f>Q3-P3</f>
+        <f t="shared" ref="Y3:Y66" si="2">Q3-P3</f>
         <v>-6.610000000000002E-2</v>
       </c>
     </row>
@@ -1472,15 +1491,15 @@
         <v>18684</v>
       </c>
       <c r="W4" s="11">
-        <f t="shared" ref="W4:W67" si="0">S4-R4</f>
+        <f t="shared" si="0"/>
         <v>1.7988999999999997</v>
       </c>
       <c r="X4" s="11">
-        <f t="shared" ref="X4:X67" si="1">U4-T4</f>
+        <f t="shared" si="1"/>
         <v>0.93080000000000007</v>
       </c>
       <c r="Y4" s="12">
-        <f t="shared" ref="Y4:Y67" si="2">Q4-P4</f>
+        <f t="shared" si="2"/>
         <v>-6.5999999999999989E-2</v>
       </c>
     </row>
@@ -1534,7 +1553,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="Q5" s="8">
-        <v>6.25E-2</v>
+        <v>-6.25E-2</v>
       </c>
       <c r="R5" s="9">
         <v>8.2372999999999994</v>
@@ -1561,7 +1580,7 @@
       </c>
       <c r="Y5" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9499999999999993E-2</v>
+        <v>-0.16449999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -1993,52 +2012,64 @@
       <c r="J11" s="6">
         <v>17</v>
       </c>
-      <c r="K11" s="2"/>
+      <c r="K11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L11" s="6">
         <v>6</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N11" s="7">
         <v>42.2</v>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P11" s="8">
         <v>3.1899999999999998E-2</v>
       </c>
-      <c r="Q11" s="2"/>
+      <c r="Q11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R11" s="9">
         <v>4.6406000000000001</v>
       </c>
-      <c r="S11" s="2"/>
+      <c r="S11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T11" s="9">
         <v>4.7678000000000003</v>
       </c>
-      <c r="U11" s="2"/>
+      <c r="U11" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V11">
         <v>21541</v>
       </c>
-      <c r="W11" s="11">
+      <c r="W11" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-4.6406000000000001</v>
-      </c>
-      <c r="X11" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X11" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-4.7678000000000003</v>
-      </c>
-      <c r="Y11" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y11" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-3.1899999999999998E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2">
         <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>24</v>
@@ -2047,7 +2078,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2">
         <v>2023</v>
@@ -2112,13 +2143,13 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2">
         <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>24</v>
@@ -2127,7 +2158,7 @@
         <v>25</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2">
         <v>2023</v>
@@ -2192,7 +2223,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2">
         <v>25</v>
@@ -2272,13 +2303,13 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2">
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
@@ -2287,7 +2318,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2">
         <v>2023</v>
@@ -2352,13 +2383,13 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>24</v>
@@ -2432,13 +2463,13 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2">
         <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>24</v>
@@ -2512,13 +2543,13 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2">
         <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
@@ -2592,13 +2623,13 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>24</v>
@@ -2619,52 +2650,64 @@
       <c r="J19" s="6">
         <v>15</v>
       </c>
-      <c r="K19" s="2"/>
+      <c r="K19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L19" s="6">
         <v>7</v>
       </c>
-      <c r="M19" s="2"/>
+      <c r="M19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N19" s="7">
         <v>48.1</v>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P19" s="8">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="Q19" s="2"/>
+      <c r="Q19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R19" s="9">
         <v>3.3517000000000001</v>
       </c>
-      <c r="S19" s="2"/>
+      <c r="S19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T19" s="9">
         <v>3.7330000000000001</v>
       </c>
-      <c r="U19" s="2"/>
+      <c r="U19" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V19">
         <v>18376</v>
       </c>
-      <c r="W19" s="11">
+      <c r="W19" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-3.3517000000000001</v>
-      </c>
-      <c r="X19" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X19" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-3.7330000000000001</v>
-      </c>
-      <c r="Y19" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y19" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-6.9500000000000006E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2">
         <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>24</v>
@@ -2738,13 +2781,13 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2">
         <v>26</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
@@ -2753,7 +2796,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="2">
         <v>2023</v>
@@ -2791,7 +2834,7 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2">
         <v>27</v>
@@ -2806,7 +2849,7 @@
         <v>33</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="2">
         <v>2023</v>
@@ -2871,7 +2914,7 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2">
         <v>27</v>
@@ -2951,13 +2994,13 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2">
         <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>24</v>
@@ -2966,7 +3009,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="2">
         <v>2023</v>
@@ -3031,13 +3074,13 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2">
         <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -3111,13 +3154,13 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2">
         <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
@@ -3191,13 +3234,13 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B27" s="2">
         <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>24</v>
@@ -3271,7 +3314,7 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" s="2">
         <v>30</v>
@@ -3351,13 +3394,13 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2">
         <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>24</v>
@@ -3431,7 +3474,7 @@
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -3511,13 +3554,13 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="2">
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>24</v>
@@ -3591,13 +3634,13 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2">
         <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>24</v>
@@ -3671,13 +3714,13 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2">
         <v>28</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>24</v>
@@ -3751,13 +3794,13 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2">
         <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>24</v>
@@ -3831,7 +3874,7 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2">
         <v>23</v>
@@ -3911,13 +3954,13 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2">
         <v>31</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>24</v>
@@ -3991,13 +4034,13 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B37" s="2">
         <v>26</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>24</v>
@@ -4071,7 +4114,7 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B38" s="2">
         <v>27</v>
@@ -4151,7 +4194,7 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" s="2">
         <v>27</v>
@@ -4231,7 +4274,7 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" s="2">
         <v>27</v>
@@ -4311,7 +4354,7 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="2">
         <v>23</v>
@@ -4379,7 +4422,7 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2">
         <v>24</v>
@@ -4394,7 +4437,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G42" s="2">
         <v>2022</v>
@@ -4459,13 +4502,13 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="2">
         <v>29</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>24</v>
@@ -4539,13 +4582,13 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2">
         <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
@@ -4566,52 +4609,64 @@
       <c r="J44" s="6">
         <v>60</v>
       </c>
-      <c r="K44" s="2"/>
+      <c r="K44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L44" s="6">
         <v>0</v>
       </c>
-      <c r="M44" s="2"/>
+      <c r="M44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N44" s="7">
         <v>52.2</v>
       </c>
-      <c r="O44" s="2"/>
+      <c r="O44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P44" s="8">
         <v>0.2455</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R44" s="9">
         <v>4.1013000000000002</v>
       </c>
-      <c r="S44" s="2"/>
+      <c r="S44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T44" s="9">
         <v>3.9575</v>
       </c>
-      <c r="U44" s="2"/>
+      <c r="U44" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V44">
         <v>16390</v>
       </c>
-      <c r="W44" s="11">
+      <c r="W44" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-4.1013000000000002</v>
-      </c>
-      <c r="X44" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X44" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-3.9575</v>
-      </c>
-      <c r="Y44" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y44" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-0.2455</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B45" s="2">
         <v>26</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>24</v>
@@ -4685,7 +4740,7 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2">
         <v>32</v>
@@ -4765,13 +4820,13 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" s="2">
         <v>35</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>24</v>
@@ -4780,7 +4835,7 @@
         <v>33</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G47" s="2">
         <v>2022</v>
@@ -4791,67 +4846,40 @@
       <c r="I47" s="4">
         <v>45139</v>
       </c>
-      <c r="J47" s="2">
-        <v>72</v>
-      </c>
-      <c r="K47" s="2">
-        <v>11</v>
-      </c>
-      <c r="L47" s="2">
-        <v>72</v>
-      </c>
-      <c r="M47" s="2">
-        <v>11</v>
-      </c>
-      <c r="N47" s="2">
-        <v>418.2</v>
-      </c>
-      <c r="O47" s="2">
-        <v>52</v>
-      </c>
-      <c r="P47" s="10">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="Q47" s="10">
-        <v>0.107</v>
-      </c>
-      <c r="R47" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="S47" s="2">
-        <v>3.46</v>
-      </c>
-      <c r="T47" s="2">
-        <v>3.46</v>
-      </c>
-      <c r="U47" s="2">
-        <v>4.91</v>
-      </c>
-      <c r="V47" s="2">
-        <v>14444</v>
-      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
       <c r="W47" s="11">
         <f t="shared" si="0"/>
-        <v>0.25999999999999979</v>
+        <v>0</v>
       </c>
       <c r="X47" s="11">
         <f t="shared" si="1"/>
-        <v>1.4500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9999999999999993E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2">
         <v>34</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>24</v>
@@ -4925,7 +4953,7 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2">
         <v>24</v>
@@ -5005,13 +5033,13 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" s="2">
         <v>31</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>24</v>
@@ -5085,13 +5113,13 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2">
         <v>26</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>24</v>
@@ -5165,13 +5193,13 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2">
         <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>24</v>
@@ -5245,7 +5273,7 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2">
         <v>29</v>
@@ -5325,13 +5353,13 @@
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B54" s="2">
         <v>30</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>24</v>
@@ -5405,13 +5433,13 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2">
         <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>24</v>
@@ -5420,7 +5448,7 @@
         <v>25</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="2">
         <v>2022</v>
@@ -5432,46 +5460,58 @@
       <c r="J55" s="6">
         <v>63</v>
       </c>
-      <c r="K55" s="2"/>
+      <c r="K55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L55" s="6">
         <v>0</v>
       </c>
-      <c r="M55" s="2"/>
+      <c r="M55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N55" s="7">
         <v>73.2</v>
       </c>
-      <c r="O55" s="2"/>
+      <c r="O55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P55" s="8">
         <v>0.15429999999999999</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R55" s="9">
         <v>5.0090000000000003</v>
       </c>
-      <c r="S55" s="2"/>
+      <c r="S55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T55" s="9">
         <v>4.5278999999999998</v>
       </c>
-      <c r="U55" s="2"/>
+      <c r="U55" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V55">
         <v>8410</v>
       </c>
-      <c r="W55" s="11">
+      <c r="W55" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-5.0090000000000003</v>
-      </c>
-      <c r="X55" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X55" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-4.5278999999999998</v>
-      </c>
-      <c r="Y55" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y55" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-0.15429999999999999</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2">
         <v>26</v>
@@ -5551,7 +5591,7 @@
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B57" s="2">
         <v>23</v>
@@ -5631,13 +5671,13 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2">
         <v>25</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>24</v>
@@ -5711,7 +5751,7 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B59" s="2">
         <v>31</v>
@@ -5738,52 +5778,64 @@
       <c r="J59" s="6">
         <v>88</v>
       </c>
-      <c r="K59" s="2"/>
+      <c r="K59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L59" s="6">
         <v>0</v>
       </c>
-      <c r="M59" s="2"/>
+      <c r="M59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N59" s="7">
         <v>80.099999999999994</v>
       </c>
-      <c r="O59" s="2"/>
+      <c r="O59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P59" s="8">
         <v>0.13270000000000001</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R59" s="9">
         <v>2.9129</v>
       </c>
-      <c r="S59" s="2"/>
+      <c r="S59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T59" s="9">
         <v>3.5255000000000001</v>
       </c>
-      <c r="U59" s="2"/>
+      <c r="U59" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V59">
         <v>12297</v>
       </c>
-      <c r="W59" s="11">
+      <c r="W59" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-2.9129</v>
-      </c>
-      <c r="X59" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X59" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-3.5255000000000001</v>
-      </c>
-      <c r="Y59" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y59" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-0.13270000000000001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B60" s="2">
         <v>25</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>24</v>
@@ -5857,13 +5909,13 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B61" s="2">
         <v>28</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>24</v>
@@ -5937,13 +5989,13 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B62" s="2">
         <v>33</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>24</v>
@@ -6017,13 +6069,13 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B63" s="2">
         <v>38</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>24</v>
@@ -6032,7 +6084,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G63" s="2">
         <v>2021</v>
@@ -6044,52 +6096,64 @@
       <c r="J63" s="6">
         <v>50</v>
       </c>
-      <c r="K63" s="2"/>
+      <c r="K63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L63" s="6">
         <v>1</v>
       </c>
-      <c r="M63" s="2"/>
+      <c r="M63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N63" s="7">
         <v>54.2</v>
       </c>
-      <c r="O63" s="2"/>
+      <c r="O63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P63" s="8">
         <v>0.13730000000000001</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R63" s="9">
         <v>5.2683</v>
       </c>
-      <c r="S63" s="2"/>
+      <c r="S63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T63" s="9">
         <v>3.98</v>
       </c>
-      <c r="U63" s="2"/>
+      <c r="U63" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V63">
         <v>9059</v>
       </c>
-      <c r="W63" s="11">
+      <c r="W63" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-5.2683</v>
-      </c>
-      <c r="X63" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X63" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-3.98</v>
-      </c>
-      <c r="Y63" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y63" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-0.13730000000000001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B64" s="2">
         <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>24</v>
@@ -6163,7 +6227,7 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B65" s="2">
         <v>27</v>
@@ -6243,7 +6307,7 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B66" s="2">
         <v>32</v>
@@ -6270,52 +6334,64 @@
       <c r="J66" s="6">
         <v>10</v>
       </c>
-      <c r="K66" s="2"/>
+      <c r="K66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L66" s="6">
         <v>3</v>
       </c>
-      <c r="M66" s="2"/>
+      <c r="M66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N66" s="7">
         <v>22</v>
       </c>
-      <c r="O66" s="2"/>
+      <c r="O66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P66" s="8">
         <v>8.5699999999999998E-2</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R66" s="9">
         <v>6.9545000000000003</v>
       </c>
-      <c r="S66" s="2"/>
+      <c r="S66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T66" s="9">
         <v>5.8</v>
       </c>
-      <c r="U66" s="2"/>
+      <c r="U66" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V66">
         <v>10547</v>
       </c>
-      <c r="W66" s="11">
+      <c r="W66" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-6.9545000000000003</v>
-      </c>
-      <c r="X66" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X66" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>-5.8</v>
-      </c>
-      <c r="Y66" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y66" s="12" t="e">
         <f t="shared" si="2"/>
-        <v>-8.5699999999999998E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B67" s="2">
         <v>28</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>24</v>
@@ -6375,21 +6451,21 @@
         <v>16207</v>
       </c>
       <c r="W67" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W67:W130" si="3">S67-R67</f>
         <v>-0.22999999999999954</v>
       </c>
       <c r="X67" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="X67:X130" si="4">U67-T67</f>
         <v>0.6897000000000002</v>
       </c>
       <c r="Y67" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Y67:Y130" si="5">Q67-P67</f>
         <v>3.9999999999999897E-3</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B68" s="2">
         <v>28</v>
@@ -6455,27 +6531,27 @@
         <v>16507</v>
       </c>
       <c r="W68" s="11">
-        <f t="shared" ref="W68:W131" si="3">S68-R68</f>
+        <f t="shared" si="3"/>
         <v>10.200399999999998</v>
       </c>
       <c r="X68" s="11">
-        <f t="shared" ref="X68:X131" si="4">U68-T68</f>
+        <f t="shared" si="4"/>
         <v>2.7987000000000002</v>
       </c>
       <c r="Y68" s="12">
-        <f t="shared" ref="Y68:Y131" si="5">Q68-P68</f>
+        <f t="shared" si="5"/>
         <v>-1.3999999999999999E-2</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B69" s="2">
         <v>28</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>24</v>
@@ -6549,7 +6625,7 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B70" s="2">
         <v>30</v>
@@ -6629,13 +6705,13 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B71" s="2">
         <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>24</v>
@@ -6709,7 +6785,7 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B72" s="2">
         <v>28</v>
@@ -6736,46 +6812,58 @@
       <c r="J72" s="6">
         <v>89</v>
       </c>
-      <c r="K72" s="2"/>
+      <c r="K72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L72" s="6">
         <v>0</v>
       </c>
-      <c r="M72" s="2"/>
+      <c r="M72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N72" s="7">
         <v>83.2</v>
       </c>
-      <c r="O72" s="2"/>
+      <c r="O72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P72" s="8">
         <v>0.2082</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R72" s="9">
         <v>2.9043999999999999</v>
       </c>
-      <c r="S72" s="2"/>
+      <c r="S72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T72" s="9">
         <v>3.2898000000000001</v>
       </c>
-      <c r="U72" s="2"/>
+      <c r="U72" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V72">
         <v>14696</v>
       </c>
-      <c r="W72" s="11">
+      <c r="W72" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-2.9043999999999999</v>
-      </c>
-      <c r="X72" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X72" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-3.2898000000000001</v>
-      </c>
-      <c r="Y72" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y72" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.2082</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B73" s="2">
         <v>23</v>
@@ -6855,7 +6943,7 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B74" s="2">
         <v>29</v>
@@ -6935,13 +7023,13 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B75" s="2">
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>24</v>
@@ -6962,52 +7050,64 @@
       <c r="J75" s="6">
         <v>5</v>
       </c>
-      <c r="K75" s="2"/>
+      <c r="K75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L75" s="6">
         <v>4</v>
       </c>
-      <c r="M75" s="2"/>
+      <c r="M75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N75" s="7">
         <v>15.2</v>
       </c>
-      <c r="O75" s="2"/>
+      <c r="O75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P75" s="8">
         <v>0.1176</v>
       </c>
-      <c r="Q75" s="2"/>
+      <c r="Q75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R75" s="9">
         <v>5.1702000000000004</v>
       </c>
-      <c r="S75" s="2"/>
+      <c r="S75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T75" s="9">
         <v>5.74</v>
       </c>
-      <c r="U75" s="2"/>
+      <c r="U75" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V75">
         <v>19942</v>
       </c>
-      <c r="W75" s="11">
+      <c r="W75" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-5.1702000000000004</v>
-      </c>
-      <c r="X75" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X75" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-5.74</v>
-      </c>
-      <c r="Y75" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y75" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1176</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B76" s="2">
         <v>31</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>24</v>
@@ -7016,7 +7116,7 @@
         <v>33</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G76" s="2">
         <v>2021</v>
@@ -7028,46 +7128,58 @@
       <c r="J76" s="6">
         <v>125</v>
       </c>
-      <c r="K76" s="2"/>
+      <c r="K76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L76" s="6">
         <v>0</v>
       </c>
-      <c r="M76" s="2"/>
+      <c r="M76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N76" s="7">
         <v>85.2</v>
       </c>
-      <c r="O76" s="2"/>
+      <c r="O76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P76" s="8">
         <v>0.1406</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R76" s="9">
         <v>4.3074000000000003</v>
       </c>
-      <c r="S76" s="2"/>
+      <c r="S76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T76" s="9">
         <v>4.0667</v>
       </c>
-      <c r="U76" s="2"/>
+      <c r="U76" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V76">
         <v>2882</v>
       </c>
-      <c r="W76" s="11">
+      <c r="W76" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-4.3074000000000003</v>
-      </c>
-      <c r="X76" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X76" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-4.0667</v>
-      </c>
-      <c r="Y76" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y76" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1406</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B77" s="2">
         <v>22</v>
@@ -7147,13 +7259,13 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B78" s="2">
         <v>32</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>24</v>
@@ -7162,7 +7274,7 @@
         <v>33</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G78" s="2">
         <v>2021</v>
@@ -7227,13 +7339,13 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B79" s="2">
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>24</v>
@@ -7307,7 +7419,7 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B80" s="2">
         <v>25</v>
@@ -7387,13 +7499,13 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B81" s="2">
         <v>27</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>24</v>
@@ -7467,13 +7579,13 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B82" s="2">
         <v>27</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>24</v>
@@ -7547,13 +7659,13 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B83" s="2">
         <v>32</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>24</v>
@@ -7627,13 +7739,13 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B84" s="2">
         <v>34</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>24</v>
@@ -7707,7 +7819,7 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" s="2">
         <v>25</v>
@@ -7734,46 +7846,58 @@
       <c r="J85" s="6">
         <v>5</v>
       </c>
-      <c r="K85" s="2"/>
+      <c r="K85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L85" s="6">
         <v>0</v>
       </c>
-      <c r="M85" s="2"/>
+      <c r="M85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N85" s="7">
         <v>4</v>
       </c>
-      <c r="O85" s="2"/>
+      <c r="O85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P85" s="8">
         <v>0.1875</v>
       </c>
-      <c r="Q85" s="2"/>
+      <c r="Q85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R85" s="9">
         <v>4.5</v>
       </c>
-      <c r="S85" s="2"/>
+      <c r="S85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T85" s="9">
         <v>1.94</v>
       </c>
-      <c r="U85" s="2"/>
+      <c r="U85" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V85">
         <v>20344</v>
       </c>
-      <c r="W85" s="11">
+      <c r="W85" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-4.5</v>
-      </c>
-      <c r="X85" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X85" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-1.94</v>
-      </c>
-      <c r="Y85" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y85" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1875</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="2">
         <v>29</v>
@@ -7853,7 +7977,7 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B87" s="2">
         <v>28</v>
@@ -7868,7 +7992,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G87" s="2">
         <v>2021</v>
@@ -7933,7 +8057,7 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B88" s="2">
         <v>25</v>
@@ -7948,7 +8072,7 @@
         <v>33</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G88" s="2">
         <v>2021</v>
@@ -8013,13 +8137,13 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B89" s="2">
         <v>26</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>24</v>
@@ -8040,52 +8164,64 @@
       <c r="J89" s="6">
         <v>5</v>
       </c>
-      <c r="K89" s="2"/>
+      <c r="K89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L89" s="6">
         <v>0</v>
       </c>
-      <c r="M89" s="2"/>
+      <c r="M89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N89" s="7">
         <v>7.1</v>
       </c>
-      <c r="O89" s="2"/>
+      <c r="O89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P89" s="8">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R89" s="9">
         <v>2.4544999999999999</v>
       </c>
-      <c r="S89" s="2"/>
+      <c r="S89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T89" s="9">
         <v>5.51</v>
       </c>
-      <c r="U89" s="2"/>
+      <c r="U89" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V89">
         <v>19582</v>
       </c>
-      <c r="W89" s="11">
+      <c r="W89" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-2.4544999999999999</v>
-      </c>
-      <c r="X89" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X89" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-5.51</v>
-      </c>
-      <c r="Y89" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y89" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-3.3300000000000003E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B90" s="2">
         <v>25</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>24</v>
@@ -8094,7 +8230,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G90" s="2">
         <v>2021</v>
@@ -8106,46 +8242,58 @@
       <c r="J90" s="6">
         <v>45</v>
       </c>
-      <c r="K90" s="2"/>
+      <c r="K90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L90" s="6">
         <v>27</v>
       </c>
-      <c r="M90" s="2"/>
+      <c r="M90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N90" s="7">
         <v>181</v>
       </c>
-      <c r="O90" s="2"/>
+      <c r="O90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P90" s="8">
         <v>6.3500000000000001E-2</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R90" s="9">
         <v>5.9668999999999999</v>
       </c>
-      <c r="S90" s="2"/>
+      <c r="S90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T90" s="9">
         <v>5.0803000000000003</v>
       </c>
-      <c r="U90" s="2"/>
+      <c r="U90" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V90">
         <v>17030</v>
       </c>
-      <c r="W90" s="11">
+      <c r="W90" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-5.9668999999999999</v>
-      </c>
-      <c r="X90" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X90" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-5.0803000000000003</v>
-      </c>
-      <c r="Y90" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y90" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-6.3500000000000001E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B91" s="2">
         <v>29</v>
@@ -8225,13 +8373,13 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B92" s="2">
         <v>23</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>24</v>
@@ -8240,7 +8388,7 @@
         <v>33</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G92" s="2">
         <v>2020</v>
@@ -8250,36 +8398,48 @@
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
+      <c r="K92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
+      <c r="M92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
+      <c r="Q92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
+      <c r="S92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
+      <c r="U92" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V92">
         <v>17581</v>
       </c>
-      <c r="W92" s="11">
+      <c r="W92" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X92" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X92" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y92" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y92" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B93" s="2">
         <v>27</v>
@@ -8359,13 +8519,13 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B94" s="2">
         <v>25</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>24</v>
@@ -8386,46 +8546,58 @@
       <c r="J94" s="6">
         <v>16</v>
       </c>
-      <c r="K94" s="2"/>
+      <c r="K94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L94" s="6">
         <v>1</v>
       </c>
-      <c r="M94" s="2"/>
+      <c r="M94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N94" s="7">
         <v>33</v>
       </c>
-      <c r="O94" s="2"/>
+      <c r="O94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P94" s="8">
         <v>7.5899999999999995E-2</v>
       </c>
-      <c r="Q94" s="2"/>
+      <c r="Q94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R94" s="9">
         <v>8.1818000000000008</v>
       </c>
-      <c r="S94" s="2"/>
+      <c r="S94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T94" s="9">
         <v>7.0503999999999998</v>
       </c>
-      <c r="U94" s="2"/>
+      <c r="U94" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V94">
         <v>18135</v>
       </c>
-      <c r="W94" s="11">
+      <c r="W94" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-8.1818000000000008</v>
-      </c>
-      <c r="X94" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X94" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-7.0503999999999998</v>
-      </c>
-      <c r="Y94" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y94" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-7.5899999999999995E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B95" s="2">
         <v>27</v>
@@ -8505,13 +8677,13 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B96" s="2">
         <v>37</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>24</v>
@@ -8585,13 +8757,13 @@
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B97" s="2">
         <v>29</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>24</v>
@@ -8665,13 +8837,13 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B98" s="2">
         <v>25</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>24</v>
@@ -8745,7 +8917,7 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B99" s="2">
         <v>23</v>
@@ -8825,13 +8997,13 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B100" s="2">
         <v>31</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>24</v>
@@ -8905,7 +9077,7 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B101" s="2">
         <v>26</v>
@@ -8985,13 +9157,13 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B102" s="2">
         <v>29</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>24</v>
@@ -9065,7 +9237,7 @@
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B103" s="2">
         <v>26</v>
@@ -9080,7 +9252,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G103" s="2">
         <v>2020</v>
@@ -9145,13 +9317,13 @@
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B104" s="2">
         <v>23</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>24</v>
@@ -9172,52 +9344,64 @@
       <c r="J104" s="6">
         <v>122</v>
       </c>
-      <c r="K104" s="2"/>
+      <c r="K104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L104" s="6">
         <v>0</v>
       </c>
-      <c r="M104" s="2"/>
+      <c r="M104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N104" s="7">
         <v>112.1</v>
       </c>
-      <c r="O104" s="2"/>
+      <c r="O104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P104" s="8">
         <v>0.1164</v>
       </c>
-      <c r="Q104" s="2"/>
+      <c r="Q104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R104" s="9">
         <v>3.3650000000000002</v>
       </c>
-      <c r="S104" s="2"/>
+      <c r="S104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T104" s="9">
         <v>3.6501999999999999</v>
       </c>
-      <c r="U104" s="2"/>
+      <c r="U104" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V104">
         <v>6832</v>
       </c>
-      <c r="W104" s="11">
+      <c r="W104" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-3.3650000000000002</v>
-      </c>
-      <c r="X104" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X104" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-3.6501999999999999</v>
-      </c>
-      <c r="Y104" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y104" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1164</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B105" s="2">
         <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>24</v>
@@ -9279,13 +9463,13 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B106" s="2">
         <v>30</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>24</v>
@@ -9359,13 +9543,13 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B107" s="2">
         <v>25</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>24</v>
@@ -9439,7 +9623,7 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B108" s="2">
         <v>26</v>
@@ -9519,7 +9703,7 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B109" s="2">
         <v>27</v>
@@ -9548,52 +9732,64 @@
       <c r="J109" s="6">
         <v>111</v>
       </c>
-      <c r="K109" s="2"/>
+      <c r="K109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L109" s="6">
         <v>0</v>
       </c>
-      <c r="M109" s="2"/>
+      <c r="M109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N109" s="7">
         <v>102.1</v>
       </c>
-      <c r="O109" s="2"/>
+      <c r="O109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P109" s="8">
         <v>0.1201</v>
       </c>
-      <c r="Q109" s="2"/>
+      <c r="Q109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R109" s="9">
         <v>4.7492000000000001</v>
       </c>
-      <c r="S109" s="2"/>
+      <c r="S109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T109" s="9">
         <v>4.1055999999999999</v>
       </c>
-      <c r="U109" s="2"/>
+      <c r="U109" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V109">
         <v>16201</v>
       </c>
-      <c r="W109" s="11">
+      <c r="W109" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-4.7492000000000001</v>
-      </c>
-      <c r="X109" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X109" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-4.1055999999999999</v>
-      </c>
-      <c r="Y109" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y109" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1201</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B110" s="2">
         <v>23</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>24</v>
@@ -9667,7 +9863,7 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B111" s="2">
         <v>26</v>
@@ -9747,7 +9943,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B112" s="2">
         <v>29</v>
@@ -9827,13 +10023,13 @@
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B113" s="2">
         <v>30</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>24</v>
@@ -9907,13 +10103,13 @@
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B114" s="2">
         <v>31</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>24</v>
@@ -9987,13 +10183,13 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B115" s="2">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>24</v>
@@ -10067,13 +10263,13 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B116" s="2">
         <v>33</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>24</v>
@@ -10147,7 +10343,7 @@
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B117" s="2">
         <v>21</v>
@@ -10162,7 +10358,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G117" s="2">
         <v>2020</v>
@@ -10227,13 +10423,13 @@
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B118" s="2">
         <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>24</v>
@@ -10307,13 +10503,13 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B119" s="2">
         <v>26</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>24</v>
@@ -10387,13 +10583,13 @@
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B120" s="2">
         <v>34</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>24</v>
@@ -10414,52 +10610,64 @@
       <c r="J120" s="6">
         <v>49</v>
       </c>
-      <c r="K120" s="2"/>
+      <c r="K120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L120" s="6">
         <v>33</v>
       </c>
-      <c r="M120" s="2"/>
+      <c r="M120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N120" s="7">
         <v>234.1</v>
       </c>
-      <c r="O120" s="2"/>
+      <c r="O120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P120" s="8">
         <v>9.4700000000000006E-2</v>
       </c>
-      <c r="Q120" s="2"/>
+      <c r="Q120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R120" s="9">
         <v>3.6871</v>
       </c>
-      <c r="S120" s="2"/>
+      <c r="S120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T120" s="9">
         <v>4.3221999999999996</v>
       </c>
-      <c r="U120" s="2"/>
+      <c r="U120" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V120">
         <v>8185</v>
       </c>
-      <c r="W120" s="11">
+      <c r="W120" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-3.6871</v>
-      </c>
-      <c r="X120" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X120" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-4.3221999999999996</v>
-      </c>
-      <c r="Y120" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y120" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-9.4700000000000006E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B121" s="2">
         <v>27</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
@@ -10533,13 +10741,13 @@
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B122" s="2">
         <v>27</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>24</v>
@@ -10613,7 +10821,7 @@
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B123" s="2">
         <v>31</v>
@@ -10640,52 +10848,64 @@
       <c r="J123" s="6">
         <v>151</v>
       </c>
-      <c r="K123" s="2"/>
+      <c r="K123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L123" s="6">
         <v>1</v>
       </c>
-      <c r="M123" s="2"/>
+      <c r="M123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N123" s="7">
         <v>174.1</v>
       </c>
-      <c r="O123" s="2"/>
+      <c r="O123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P123" s="8">
         <v>0.13</v>
       </c>
-      <c r="Q123" s="2"/>
+      <c r="Q123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R123" s="9">
         <v>3.4588999999999999</v>
       </c>
-      <c r="S123" s="2"/>
+      <c r="S123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T123" s="9">
         <v>4.0766999999999998</v>
       </c>
-      <c r="U123" s="2"/>
+      <c r="U123" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V123">
         <v>9029</v>
       </c>
-      <c r="W123" s="11">
+      <c r="W123" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-3.4588999999999999</v>
-      </c>
-      <c r="X123" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X123" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-4.0766999999999998</v>
-      </c>
-      <c r="Y123" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y123" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.13</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B124" s="2">
         <v>34</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>24</v>
@@ -10759,13 +10979,13 @@
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B125" s="2">
         <v>29</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>24</v>
@@ -10786,46 +11006,58 @@
       <c r="J125" s="6">
         <v>74</v>
       </c>
-      <c r="K125" s="2"/>
+      <c r="K125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L125" s="6">
         <v>0</v>
       </c>
-      <c r="M125" s="2"/>
+      <c r="M125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N125" s="7">
         <v>87.1</v>
       </c>
-      <c r="O125" s="2"/>
+      <c r="O125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P125" s="8">
         <v>0.1016</v>
       </c>
-      <c r="Q125" s="2"/>
+      <c r="Q125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R125" s="9">
         <v>3.7099000000000002</v>
       </c>
-      <c r="S125" s="2"/>
+      <c r="S125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T125" s="9">
         <v>4.5582000000000003</v>
       </c>
-      <c r="U125" s="2"/>
+      <c r="U125" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V125">
         <v>12452</v>
       </c>
-      <c r="W125" s="11">
+      <c r="W125" s="11" t="e">
         <f t="shared" si="3"/>
-        <v>-3.7099000000000002</v>
-      </c>
-      <c r="X125" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X125" s="11" t="e">
         <f t="shared" si="4"/>
-        <v>-4.5582000000000003</v>
-      </c>
-      <c r="Y125" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y125" s="12" t="e">
         <f t="shared" si="5"/>
-        <v>-0.1016</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B126" s="2">
         <v>27</v>
@@ -10905,7 +11137,7 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B127" s="2">
         <v>24</v>
@@ -10985,13 +11217,13 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B128" s="2">
         <v>22</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>24</v>
@@ -11065,7 +11297,7 @@
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B129" s="2">
         <v>25</v>
@@ -11145,7 +11377,7 @@
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B130" s="2">
         <v>26</v>
@@ -11225,13 +11457,13 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B131" s="2">
         <v>27</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>24</v>
@@ -11291,27 +11523,27 @@
         <v>15010</v>
       </c>
       <c r="W131" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W131:W159" si="6">S131-R131</f>
         <v>0.58639999999999981</v>
       </c>
       <c r="X131" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="X131:X159" si="7">U131-T131</f>
         <v>1.4229000000000003</v>
       </c>
       <c r="Y131" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="Y131:Y159" si="8">Q131-P131</f>
         <v>-0.14219999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B132" s="2">
         <v>26</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>24</v>
@@ -11371,21 +11603,21 @@
         <v>13218</v>
       </c>
       <c r="W132" s="11">
-        <f t="shared" ref="W132:W159" si="6">S132-R132</f>
+        <f t="shared" si="6"/>
         <v>0.32739999999999947</v>
       </c>
       <c r="X132" s="11">
-        <f t="shared" ref="X132:X159" si="7">U132-T132</f>
+        <f t="shared" si="7"/>
         <v>0.14829999999999988</v>
       </c>
       <c r="Y132" s="12">
-        <f t="shared" ref="Y132:Y159" si="8">Q132-P132</f>
+        <f t="shared" si="8"/>
         <v>1.1399999999999993E-2</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B133" s="2">
         <v>26</v>
@@ -11400,7 +11632,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G133" s="2">
         <v>2019</v>
@@ -11465,13 +11697,13 @@
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B134" s="2">
         <v>25</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>24</v>
@@ -11545,13 +11777,13 @@
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B135" s="2">
         <v>28</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>24</v>
@@ -11625,13 +11857,13 @@
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B136" s="2">
         <v>24</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>24</v>
@@ -11705,7 +11937,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B137" s="2">
         <v>26</v>
@@ -11785,13 +12017,13 @@
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B138" s="2">
         <v>27</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>24</v>
@@ -11810,31 +12042,43 @@
       </c>
       <c r="I138" s="4"/>
       <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
+      <c r="K138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
+      <c r="M138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P138" s="2"/>
-      <c r="Q138" s="2"/>
+      <c r="Q138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R138" s="2"/>
-      <c r="S138" s="2"/>
+      <c r="S138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T138" s="2"/>
-      <c r="U138" s="2"/>
+      <c r="U138" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V138">
         <v>17126</v>
       </c>
-      <c r="W138" s="11">
+      <c r="W138" s="11" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X138" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X138" s="11" t="e">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y138" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y138" s="12" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.35">
@@ -11907,7 +12151,7 @@
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B140" s="2">
         <v>25</v>
@@ -11987,7 +12231,7 @@
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B141" s="2">
         <v>22</v>
@@ -12055,13 +12299,13 @@
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B142" s="2">
         <v>26</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>24</v>
@@ -12135,13 +12379,13 @@
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B143" s="2">
         <v>32</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>24</v>
@@ -12215,13 +12459,13 @@
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B144" s="2">
         <v>25</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>24</v>
@@ -12242,52 +12486,64 @@
       <c r="J144" s="6">
         <v>18</v>
       </c>
-      <c r="K144" s="2"/>
+      <c r="K144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L144" s="6">
         <v>18</v>
       </c>
-      <c r="M144" s="2"/>
+      <c r="M144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N144" s="7">
         <v>91.1</v>
       </c>
-      <c r="O144" s="2"/>
+      <c r="O144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P144" s="8">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="Q144" s="2"/>
+      <c r="Q144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R144" s="9">
         <v>6.1094999999999997</v>
       </c>
-      <c r="S144" s="2"/>
+      <c r="S144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T144" s="9">
         <v>5.59</v>
       </c>
-      <c r="U144" s="2"/>
+      <c r="U144" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V144">
         <v>16164</v>
       </c>
-      <c r="W144" s="11">
+      <c r="W144" s="11" t="e">
         <f t="shared" si="6"/>
-        <v>-6.1094999999999997</v>
-      </c>
-      <c r="X144" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X144" s="11" t="e">
         <f t="shared" si="7"/>
-        <v>-5.59</v>
-      </c>
-      <c r="Y144" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y144" s="12" t="e">
         <f t="shared" si="8"/>
-        <v>-9.9000000000000005E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B145" s="2">
         <v>28</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>24</v>
@@ -12361,7 +12617,7 @@
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B146" s="2">
         <v>30</v>
@@ -12441,7 +12697,7 @@
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B147" s="2">
         <v>27</v>
@@ -12468,52 +12724,64 @@
       <c r="J147" s="6">
         <v>24</v>
       </c>
-      <c r="K147" s="2"/>
+      <c r="K147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L147" s="6">
         <v>24</v>
       </c>
-      <c r="M147" s="2"/>
+      <c r="M147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N147" s="7">
         <v>119.2</v>
       </c>
-      <c r="O147" s="2"/>
+      <c r="O147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P147" s="8">
         <v>0.1227</v>
       </c>
-      <c r="Q147" s="2"/>
+      <c r="Q147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R147" s="9">
         <v>6.1670999999999996</v>
       </c>
-      <c r="S147" s="2"/>
+      <c r="S147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T147" s="9">
         <v>4.9203999999999999</v>
       </c>
-      <c r="U147" s="2"/>
+      <c r="U147" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V147">
         <v>8493</v>
       </c>
-      <c r="W147" s="11">
+      <c r="W147" s="11" t="e">
         <f t="shared" si="6"/>
-        <v>-6.1670999999999996</v>
-      </c>
-      <c r="X147" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X147" s="11" t="e">
         <f t="shared" si="7"/>
-        <v>-4.9203999999999999</v>
-      </c>
-      <c r="Y147" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y147" s="12" t="e">
         <f t="shared" si="8"/>
-        <v>-0.1227</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B148" s="2">
         <v>29</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>24</v>
@@ -12534,52 +12802,64 @@
       <c r="J148" s="6">
         <v>26</v>
       </c>
-      <c r="K148" s="2"/>
+      <c r="K148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L148" s="6">
         <v>0</v>
       </c>
-      <c r="M148" s="2"/>
+      <c r="M148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N148" s="7">
         <v>30.2</v>
       </c>
-      <c r="O148" s="2"/>
+      <c r="O148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P148" s="8">
         <v>0.1852</v>
       </c>
-      <c r="Q148" s="2"/>
+      <c r="Q148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R148" s="9">
         <v>4.6957000000000004</v>
       </c>
-      <c r="S148" s="2"/>
+      <c r="S148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T148" s="9">
         <v>4.79</v>
       </c>
-      <c r="U148" s="2"/>
+      <c r="U148" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V148">
         <v>11012</v>
       </c>
-      <c r="W148" s="11">
+      <c r="W148" s="11" t="e">
         <f t="shared" si="6"/>
-        <v>-4.6957000000000004</v>
-      </c>
-      <c r="X148" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X148" s="11" t="e">
         <f t="shared" si="7"/>
-        <v>-4.79</v>
-      </c>
-      <c r="Y148" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y148" s="12" t="e">
         <f t="shared" si="8"/>
-        <v>-0.1852</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B149" s="2">
         <v>25</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>24</v>
@@ -12653,7 +12933,7 @@
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B150" s="2">
         <v>32</v>
@@ -12680,46 +12960,58 @@
       <c r="J150" s="6">
         <v>142</v>
       </c>
-      <c r="K150" s="2"/>
+      <c r="K150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="L150" s="6">
         <v>0</v>
       </c>
-      <c r="M150" s="2"/>
+      <c r="M150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="N150" s="7">
         <v>151</v>
       </c>
-      <c r="O150" s="2"/>
+      <c r="O150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="P150" s="8">
         <v>0.14199999999999999</v>
       </c>
-      <c r="Q150" s="2"/>
+      <c r="Q150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="R150" s="9">
         <v>4.7085999999999997</v>
       </c>
-      <c r="S150" s="2"/>
+      <c r="S150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="T150" s="9">
         <v>3.8984999999999999</v>
       </c>
-      <c r="U150" s="2"/>
+      <c r="U150" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="V150">
         <v>1345</v>
       </c>
-      <c r="W150" s="11">
+      <c r="W150" s="11" t="e">
         <f t="shared" si="6"/>
-        <v>-4.7085999999999997</v>
-      </c>
-      <c r="X150" s="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X150" s="11" t="e">
         <f t="shared" si="7"/>
-        <v>-3.8984999999999999</v>
-      </c>
-      <c r="Y150" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y150" s="12" t="e">
         <f t="shared" si="8"/>
-        <v>-0.14199999999999999</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B151" s="2">
         <v>24</v>
@@ -12799,7 +13091,7 @@
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B152" s="2">
         <v>25</v>
@@ -12879,7 +13171,7 @@
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B153" s="2">
         <v>25</v>
@@ -12959,7 +13251,7 @@
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B154" s="2">
         <v>29</v>
@@ -12974,7 +13266,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G154" s="2">
         <v>2018</v>
@@ -13039,13 +13331,13 @@
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B155" s="2">
         <v>26</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>24</v>
@@ -13119,13 +13411,13 @@
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B156" s="2">
         <v>27</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>24</v>
@@ -13199,13 +13491,13 @@
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B157" s="2">
         <v>31</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>24</v>
@@ -13279,13 +13571,13 @@
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B158" s="2">
         <v>26</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>24</v>
@@ -13294,7 +13586,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G158" s="2">
         <v>2018</v>
@@ -13359,7 +13651,7 @@
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B159" s="2">
         <v>28</v>
@@ -13436,6 +13728,12 @@
         <f t="shared" si="8"/>
         <v>4.1599999999999998E-2</v>
       </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A160" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="W160" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13455,16 +13753,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -13475,10 +13773,10 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -13486,13 +13784,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -13500,13 +13798,13 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -13514,13 +13812,13 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -13528,13 +13826,13 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -13542,13 +13840,13 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -13556,13 +13854,13 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -13570,13 +13868,13 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -13584,13 +13882,13 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -13598,13 +13896,13 @@
         <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -13612,13 +13910,13 @@
         <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -13626,13 +13924,13 @@
         <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -13640,13 +13938,13 @@
         <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -13654,13 +13952,13 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -13668,13 +13966,13 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -13682,13 +13980,13 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -13696,13 +13994,13 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -13710,13 +14008,13 @@
         <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -13724,13 +14022,13 @@
         <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -13738,13 +14036,13 @@
         <v>104</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -13752,13 +14050,13 @@
         <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -13766,13 +14064,13 @@
         <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -13780,13 +14078,13 @@
         <v>120</v>
       </c>
       <c r="B24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -13794,13 +14092,13 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -13808,13 +14106,13 @@
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -13822,13 +14120,13 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -13836,13 +14134,13 @@
         <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -13853,10 +14151,10 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -13864,13 +14162,13 @@
         <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -13878,13 +14176,13 @@
         <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -13892,13 +14190,13 @@
         <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -13906,13 +14204,13 @@
         <v>148</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -13920,13 +14218,13 @@
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
